--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDF0078-2762-4AF9-AFFD-32AACC7B8B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C92FB40-DC83-4849-BCB5-2AB0AFF17E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -1834,83 +1834,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>13</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="U2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="V2" s="1">
+      <c r="AJ2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -1977,83 +1977,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>20</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="T3" s="1">
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="V3" s="1">
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AK3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2122,83 +2122,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="T4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="U4" s="1">
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="V4" s="1">
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AA4" s="1">
+      <c r="AK4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2271,83 +2271,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="U5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
       <c r="V5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="W5" s="1">
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="X5" s="1">
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AI5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AJ5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="Y5" s="1">
+      <c r="AK5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AL5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -2420,83 +2420,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="W6" s="1">
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AH6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="X6" s="1">
+      <c r="AI6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AG6" s="1">
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AK6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -2560,83 +2560,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="U7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="V7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Z7" s="1">
+      <c r="AC7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AG7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AH7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -2707,83 +2707,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="T8" s="1">
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="U8" s="1">
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AH8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AC8" s="1">
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AL8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -2847,83 +2847,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="U9" s="1">
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AA9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z9" s="1">
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AJ9" s="1">
+      <c r="AK9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -2993,83 +2993,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
       <c r="Z10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
       <c r="AH10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3132,83 +3132,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="W11" s="1">
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AI11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE11" s="1">
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AK11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -3274,83 +3274,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="V12" s="1">
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="X12" s="1">
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AE12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="Y12" s="1">
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AK12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -3413,83 +3413,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA13" s="1">
+      <c r="AH13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
       <c r="AI13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -3556,83 +3556,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="T14" s="1">
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AJ14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="U14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="V14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W14" s="1">
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -3695,83 +3695,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -3834,63 +3834,63 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -3902,15 +3902,15 @@
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -3926,7 +3926,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -3971,7 +3971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>5</v>
@@ -4036,7 +4036,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -4112,7 +4112,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -4174,8 +4174,11 @@
       <c r="AS20">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU20">
+        <v>401926.91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4227,8 +4230,11 @@
       <c r="AS21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU21">
+        <v>6371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="O22" s="1" t="s">
         <v>41</v>
       </c>
@@ -4244,8 +4250,11 @@
       <c r="AS22">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU22">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>20</v>
       </c>
@@ -4280,7 +4289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -4317,8 +4326,12 @@
       <c r="AS24">
         <v>39</v>
       </c>
-    </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU24">
+        <f>AU20/(AU22*AU22)</f>
+        <v>6778.9999999999991</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="O25" s="1" t="s">
         <v>31</v>
       </c>
@@ -4334,8 +4347,12 @@
       <c r="AS25">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU25">
+        <f>AU24-AU21</f>
+        <v>407.99999999999909</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="L26" t="s">
         <v>50</v>
       </c>
@@ -4361,8 +4378,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="C29" s="12">
         <v>3</v>
       </c>
@@ -4380,7 +4397,7 @@
       </c>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="C30" s="14"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
@@ -4390,7 +4407,7 @@
       <c r="I30" s="15"/>
       <c r="J30" s="17"/>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="C31" s="22">
         <v>4</v>
       </c>
@@ -4408,7 +4425,7 @@
       </c>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="24"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
@@ -4512,6 +4529,7 @@
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
     <col min="2" max="17" width="3.28515625" customWidth="1"/>
+    <col min="18" max="18" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
@@ -5490,11 +5508,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H28:I29"/>
     <mergeCell ref="B28:C29"/>
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="B22:C23"/>
     <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -5506,9 +5524,9 @@
     <mergeCell ref="K23:Q28"/>
     <mergeCell ref="F26:G27"/>
     <mergeCell ref="H26:I27"/>
-    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C92FB40-DC83-4849-BCB5-2AB0AFF17E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761558FA-06F1-423D-BFB9-E802BE67BE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -387,9 +387,6 @@
     <t>h=</t>
   </si>
   <si>
-    <t>+ O N E</t>
-  </si>
-  <si>
     <t>Printer Margins</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t>Cs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + S I X</t>
   </si>
 </sst>
 </file>
@@ -711,22 +711,49 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -741,40 +768,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1495,69 +1495,69 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9">
         <v>3.4</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10">
         <v>16.7</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
         <v>122</v>
-      </c>
-      <c r="B13" t="s">
-        <v>123</v>
       </c>
       <c r="C13">
         <v>13.9</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E13">
         <f>C13-(C8+C10)/10</f>
         <v>11.93</v>
       </c>
       <c r="F13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13">
         <f>E13*3</f>
@@ -1567,7 +1567,7 @@
         <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -1583,20 +1583,20 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>21.3</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E14">
         <f>C14-2*C9/10</f>
         <v>20.62</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14">
         <f>E14*3</f>
@@ -1606,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -1834,83 +1834,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V2" s="1">
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
       <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
       <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -1977,83 +1977,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="U3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="V3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="W3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="Z3" s="1">
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AJ3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2122,83 +2122,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AC4" s="1">
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
       <c r="AK4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2271,83 +2271,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="X5" s="1">
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AF5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="Y5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
       <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AH5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AJ5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -2420,83 +2420,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
-      </c>
-      <c r="T6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="U6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -2560,83 +2560,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AH7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="T7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="V7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AJ7" s="1">
+      <c r="AK7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AL7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -2707,83 +2707,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="U8" s="1">
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Z8" s="1">
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AL8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -2847,83 +2847,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="U9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V9" s="1">
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AC9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD9" s="1">
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AK9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -2993,83 +2993,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y10" s="1">
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
       <c r="AG10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3132,51 +3132,51 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>26</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="V11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
       <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AB11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AC11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3184,31 +3184,31 @@
       </c>
       <c r="AF11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AG11" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
       <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -3217,7 +3217,7 @@
         <v>11</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
@@ -3274,83 +3274,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="V12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AF12" s="1">
+      <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -3413,83 +3413,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -3498,8 +3498,8 @@
         <v>13</v>
       </c>
       <c r="AS13" s="7">
-        <f>AS9+1</f>
-        <v>409</v>
+        <f>AS9+6</f>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.25">
@@ -3556,83 +3556,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="U14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="V14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Z14" s="1">
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AE14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC14" s="1">
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG14" s="1">
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -3695,83 +3695,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="W15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -3834,15 +3834,15 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -3850,15 +3850,15 @@
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -3866,47 +3866,47 @@
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3919,7 +3919,7 @@
         <v>16</v>
       </c>
       <c r="AR16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AT16">
         <f>SUM(AS18:AS26)</f>
@@ -4106,7 +4106,7 @@
         <v>19</v>
       </c>
       <c r="AR19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AS19">
         <v>102</v>
@@ -4342,7 +4342,7 @@
         <v>25</v>
       </c>
       <c r="AR25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AS25">
         <v>14</v>
@@ -4372,7 +4372,7 @@
         <v>26</v>
       </c>
       <c r="AR26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AS26">
         <v>55</v>
@@ -4380,116 +4380,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="12">
+      <c r="C29" s="26">
         <v>3</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13">
+      <c r="D29" s="16"/>
+      <c r="E29" s="16">
         <v>1</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="18">
+      <c r="F29" s="17"/>
+      <c r="G29" s="27">
         <v>4</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="13">
+      <c r="H29" s="28"/>
+      <c r="I29" s="16">
         <v>2</v>
       </c>
-      <c r="J29" s="16"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="17"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="22">
+      <c r="C31" s="14">
         <v>4</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23">
+      <c r="D31" s="15"/>
+      <c r="E31" s="15">
         <v>2</v>
       </c>
-      <c r="F31" s="26"/>
-      <c r="G31" s="14">
+      <c r="F31" s="21"/>
+      <c r="G31" s="22">
         <v>3</v>
       </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="23">
+      <c r="H31" s="18"/>
+      <c r="I31" s="15">
         <v>1</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="21"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="27"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="33"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="30">
+      <c r="C33" s="12">
         <v>1</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="13">
+      <c r="D33" s="13"/>
+      <c r="E33" s="16">
         <v>3</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="30">
+      <c r="F33" s="17"/>
+      <c r="G33" s="12">
         <v>2</v>
       </c>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31">
+      <c r="H33" s="13"/>
+      <c r="I33" s="13">
         <v>4</v>
       </c>
-      <c r="J33" s="32"/>
+      <c r="J33" s="20"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="22"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="26"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="21"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="14">
+      <c r="C35" s="22">
         <v>2</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18">
         <v>4</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="14">
+      <c r="F35" s="19"/>
+      <c r="G35" s="22">
         <v>1</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15">
+      <c r="H35" s="18"/>
+      <c r="I35" s="18">
         <v>3</v>
       </c>
-      <c r="J35" s="17"/>
+      <c r="J35" s="19"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="33"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="25"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -4498,6 +4498,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:F34"/>
     <mergeCell ref="G33:H34"/>
@@ -4506,14 +4514,6 @@
     <mergeCell ref="E35:F36"/>
     <mergeCell ref="G35:H36"/>
     <mergeCell ref="I35:J36"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5371,24 +5371,24 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="16"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
       <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
@@ -5400,20 +5400,20 @@
       <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="B24" s="22">
         <v>4</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15">
+      <c r="C24" s="18"/>
+      <c r="D24" s="18">
         <v>2</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15">
+      <c r="E24" s="19"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18">
         <v>1</v>
       </c>
-      <c r="I24" s="17"/>
+      <c r="I24" s="19"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
@@ -5423,14 +5423,14 @@
       <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="33"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="25"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
@@ -5440,20 +5440,20 @@
       <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
+      <c r="B26" s="26">
         <v>1</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="12">
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="26">
         <v>2</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13">
+      <c r="G26" s="16"/>
+      <c r="H26" s="16">
         <v>4</v>
       </c>
-      <c r="I26" s="16"/>
+      <c r="I26" s="17"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35"/>
@@ -5463,14 +5463,14 @@
       <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="17"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="35"/>
@@ -5480,14 +5480,14 @@
       <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="17"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
       <c r="M28" s="35"/>
@@ -5497,22 +5497,17 @@
       <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -5527,6 +5522,11 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6384,32 +6384,32 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="12">
+      <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18">
+      <c r="E22" s="17"/>
+      <c r="F22" s="27">
         <v>4</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13">
+      <c r="G22" s="28"/>
+      <c r="H22" s="16">
         <v>2</v>
       </c>
-      <c r="I22" s="16"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
       <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
@@ -6421,22 +6421,22 @@
       <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22">
+      <c r="B24" s="14">
         <v>4</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15">
         <v>2</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="14">
+      <c r="E24" s="21"/>
+      <c r="F24" s="22">
         <v>3</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="23">
+      <c r="G24" s="18"/>
+      <c r="H24" s="15">
         <v>1</v>
       </c>
-      <c r="I24" s="26"/>
+      <c r="I24" s="21"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
@@ -6446,14 +6446,14 @@
       <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="27"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
@@ -6463,22 +6463,22 @@
       <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30">
+      <c r="B26" s="12">
         <v>1</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="13">
+      <c r="C26" s="13"/>
+      <c r="D26" s="16">
         <v>3</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="30">
+      <c r="E26" s="17"/>
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31">
+      <c r="G26" s="13"/>
+      <c r="H26" s="13">
         <v>4</v>
       </c>
-      <c r="I26" s="32"/>
+      <c r="I26" s="20"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35"/>
@@ -6488,14 +6488,14 @@
       <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="26"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="21"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="35"/>
@@ -6505,22 +6505,22 @@
       <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+      <c r="B28" s="22">
         <v>2</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15">
+      <c r="C28" s="18"/>
+      <c r="D28" s="18">
         <v>4</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14">
+      <c r="E28" s="19"/>
+      <c r="F28" s="22">
         <v>1</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15">
+      <c r="G28" s="18"/>
+      <c r="H28" s="18">
         <v>3</v>
       </c>
-      <c r="I28" s="17"/>
+      <c r="I28" s="19"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
       <c r="M28" s="35"/>
@@ -6530,14 +6530,14 @@
       <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25"/>
       <c r="K29" s="36" t="s">
         <v>58</v>
       </c>
@@ -6565,6 +6565,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="F24:G25"/>
     <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
     <mergeCell ref="B26:C27"/>
@@ -6575,16 +6585,6 @@
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="F24:G25"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761558FA-06F1-423D-BFB9-E802BE67BE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB41CFF-20F5-4CBA-B6E9-3D56D7A9A597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="2" r:id="rId1"/>
-    <sheet name="Draft" sheetId="1" r:id="rId2"/>
-    <sheet name="Word_Search" sheetId="3" r:id="rId3"/>
-    <sheet name="Word_Search_solution" sheetId="4" r:id="rId4"/>
-    <sheet name="Riddle" sheetId="5" r:id="rId5"/>
+    <sheet name="Adventure Tracker" sheetId="7" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="Info" sheetId="2" r:id="rId3"/>
+    <sheet name="Draft" sheetId="1" r:id="rId4"/>
+    <sheet name="Word_Search" sheetId="3" r:id="rId5"/>
+    <sheet name="Word_Search_solution" sheetId="4" r:id="rId6"/>
+    <sheet name="Riddle" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="184">
   <si>
     <t>Line/Column</t>
   </si>
@@ -433,6 +435,199 @@
   </si>
   <si>
     <t xml:space="preserve"> + S I X</t>
+  </si>
+  <si>
+    <t>🎒 Backpack Adventure – Master Tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🟦 Items needed now (used at this stage)     🟨 Items received early but used later     🟩 Solution logic     🟧 Code / Answer     🟪 Unlocks</t>
+  </si>
+  <si>
+    <t>── LOCATION ──</t>
+  </si>
+  <si>
+    <t>── ITEMS ──</t>
+  </si>
+  <si>
+    <t>── PUZZLE ──</t>
+  </si>
+  <si>
+    <t>── ANSWER ──</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Stage Name</t>
+  </si>
+  <si>
+    <t>Location
+in Bag</t>
+  </si>
+  <si>
+    <t>← Comes
+From Stage</t>
+  </si>
+  <si>
+    <t>Items Used
+Here
+(needed now)</t>
+  </si>
+  <si>
+    <t>Items
+Received Here
+(used later →)</t>
+  </si>
+  <si>
+    <t>Puzzle /
+Challenge</t>
+  </si>
+  <si>
+    <t>Solution Logic</t>
+  </si>
+  <si>
+    <t>Code /
+Answer</t>
+  </si>
+  <si>
+    <t>Unlocks →</t>
+  </si>
+  <si>
+    <t>Difficulty
+(1–5)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Start of Backpack</t>
+  </si>
+  <si>
+    <t>Main compartment
+(top)</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>Water bottle + stickers
+Welcome card with QR code</t>
+  </si>
+  <si>
+    <t>Hidden numbers in
+animal stickers</t>
+  </si>
+  <si>
+    <t>Each sticker animal's geological era → one digit
+(order of eras = order of digits)</t>
+  </si>
+  <si>
+    <t>7  4  9</t>
+  </si>
+  <si>
+    <t>Front Compartment</t>
+  </si>
+  <si>
+    <t>✅ Done</t>
+  </si>
+  <si>
+    <t>Front zip
+compartment</t>
+  </si>
+  <si>
+    <t>Note card (ADHD &amp; Plushy)
+Word search + sudoku page</t>
+  </si>
+  <si>
+    <t>Lego number (0 blue)
+Lego hobbies pieces
+Sticker with IV blue
+→ used in Stage 4</t>
+  </si>
+  <si>
+    <t>Word search + sudoku
+combo puzzle</t>
+  </si>
+  <si>
+    <t>Words in search draw digits 7 &amp; 3;
+highlighted sudoku box = 4</t>
+  </si>
+  <si>
+    <t>7  3  4</t>
+  </si>
+  <si>
+    <t>Front Pocket</t>
+  </si>
+  <si>
+    <t>Items for later placed here so player carries them without knowing why</t>
+  </si>
+  <si>
+    <t>Small front
+pocket</t>
+  </si>
+  <si>
+    <t>Card from grandparents
+News article about dog</t>
+  </si>
+  <si>
+    <t>Value of v (on back
+of news clipping)
+→ used in Stage 4</t>
+  </si>
+  <si>
+    <t>Find the dog's name
+on collar in photo</t>
+  </si>
+  <si>
+    <t>Dog collar in news article photo clearly reads MOON</t>
+  </si>
+  <si>
+    <t>M O O N</t>
+  </si>
+  <si>
+    <t>Large Compartment</t>
+  </si>
+  <si>
+    <t>Easy breather before the final hard stage</t>
+  </si>
+  <si>
+    <t>Main large
+compartment</t>
+  </si>
+  <si>
+    <t>Lego pieces from Stage 2
+Value of v from Stage 3</t>
+  </si>
+  <si>
+    <t>Periodic table
+Note about stars and ISS
+Calculator</t>
+  </si>
+  <si>
+    <t>Locked pouch + final bag
+ISS instructions + Note
+Lego cube
+Lego jobs pieces</t>
+  </si>
+  <si>
+    <t>Periodic table element
+lookup from ISS note</t>
+  </si>
+  <si>
+    <t>Sum atomic numbers of elements in ISS note
+(KNoWN PHYSiCS). Requires calculator + periodic table</t>
+  </si>
+  <si>
+    <t>6  2  3</t>
+  </si>
+  <si>
+    <t>Top Pocket (END 🎉)</t>
+  </si>
+  <si>
+    <t>Hardest stage — player must use items collected in stages 2 &amp; 3</t>
   </si>
 </sst>
 </file>
@@ -443,7 +638,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,8 +700,72 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF7D5800"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFAAAAAA"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -536,8 +795,78 @@
         <fgColor theme="8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2C3E6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3A7DBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8960C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E7D52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8560A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E35A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE8C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -680,13 +1009,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0C4DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -711,49 +1055,22 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -768,13 +1085,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -785,6 +1129,94 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1468,6 +1900,328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF98571C-67F3-4A93-A173-F5ACBB578192}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+    </row>
+    <row r="4" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="L4" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="M4" s="41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>1</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="I5" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="J5" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="K5" s="55">
+        <v>3</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" s="56"/>
+    </row>
+    <row r="6" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57">
+        <v>2</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="K6" s="61">
+        <v>3</v>
+      </c>
+      <c r="L6" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6" s="62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47">
+        <v>3</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="K7" s="55">
+        <v>2</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="M7" s="56" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="57">
+        <v>4</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="J8" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" s="61">
+        <v>4</v>
+      </c>
+      <c r="L8" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="M8" s="62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="63">
+        <v>5</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="K5:K9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="L5:L9" xr:uid="{4D7E9BDF-04E7-4D7D-A558-7BBC5E7910BC}">
+      <formula1>"🔲 Not Started,🔧 In Progress,✅ Done,⏸ On Hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBB895D-374E-47E9-B67F-28D3C51CD256}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D260E2E-9366-4C07-AD85-6CF609B51D36}">
   <dimension ref="A2:M17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1644,7 +2398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -1834,83 +2588,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="W2" s="1">
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AF2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AA2" s="1">
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI2" s="1">
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -1977,83 +2731,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>11</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="T3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="V3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="X3" s="1">
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI3" s="1">
+      <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2122,83 +2876,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="V4" s="1">
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="X4" s="1">
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AI4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AF4" s="1">
+      <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
       <c r="AK4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2271,79 +3025,79 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AG5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AI5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="U5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="V5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="X5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="AJ5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -2420,83 +3174,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="V6" s="1">
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="W6" s="1">
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="X6" s="1">
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -2560,83 +3314,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="T7" s="1">
+      <c r="AB7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="U7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="V7" s="1">
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF7" s="1">
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
       <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -2707,83 +3461,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA8" s="1">
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
       <c r="AJ8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -2847,83 +3601,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="T9" s="1">
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="U9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="AK9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -2997,79 +3751,79 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="U10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AA10" s="1">
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AJ10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
       <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3132,83 +3886,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Z11" s="1">
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AK11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AL11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -3274,79 +4028,79 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
       <c r="AI12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3413,83 +4167,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X13" s="1">
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AK13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AL13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -3556,83 +4310,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="U14" s="1">
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="V14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="W14" s="1">
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -3695,83 +4449,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="T15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="U15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="V15" s="1">
+      <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
-      </c>
-      <c r="W15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Z15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -3834,83 +4588,83 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -4380,116 +5134,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="26">
+      <c r="C29" s="12">
         <v>3</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16">
+      <c r="D29" s="13"/>
+      <c r="E29" s="13">
         <v>1</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="27">
+      <c r="F29" s="16"/>
+      <c r="G29" s="18">
         <v>4</v>
       </c>
-      <c r="H29" s="28"/>
-      <c r="I29" s="16">
+      <c r="H29" s="19"/>
+      <c r="I29" s="13">
         <v>2</v>
       </c>
-      <c r="J29" s="17"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="22"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="19"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="14">
+      <c r="C31" s="22">
         <v>4</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15">
+      <c r="D31" s="23"/>
+      <c r="E31" s="23">
         <v>2</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="22">
+      <c r="F31" s="26"/>
+      <c r="G31" s="14">
         <v>3</v>
       </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="15">
+      <c r="H31" s="15"/>
+      <c r="I31" s="23">
         <v>1</v>
       </c>
-      <c r="J31" s="21"/>
+      <c r="J31" s="26"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="27"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="12">
+      <c r="C33" s="30">
         <v>1</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="16">
+      <c r="D33" s="31"/>
+      <c r="E33" s="13">
         <v>3</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="12">
+      <c r="F33" s="16"/>
+      <c r="G33" s="30">
         <v>2</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13">
+      <c r="H33" s="31"/>
+      <c r="I33" s="31">
         <v>4</v>
       </c>
-      <c r="J33" s="20"/>
+      <c r="J33" s="32"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="21"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="22">
+      <c r="C35" s="14">
         <v>2</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18">
+      <c r="D35" s="15"/>
+      <c r="E35" s="15">
         <v>4</v>
       </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="22">
+      <c r="F35" s="17"/>
+      <c r="G35" s="14">
         <v>1</v>
       </c>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18">
+      <c r="H35" s="15"/>
+      <c r="I35" s="15">
         <v>3</v>
       </c>
-      <c r="J35" s="19"/>
+      <c r="J35" s="17"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="25"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -4498,6 +5252,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
     <mergeCell ref="C29:D30"/>
     <mergeCell ref="E29:F30"/>
     <mergeCell ref="G29:H30"/>
@@ -4506,20 +5268,12 @@
     <mergeCell ref="E31:F32"/>
     <mergeCell ref="G31:H32"/>
     <mergeCell ref="I31:J32"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D804ABF-C663-46F7-972D-D3A53183DCD1}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -5371,24 +6125,24 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="26"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="19"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="17"/>
       <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
@@ -5400,20 +6154,20 @@
       <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="22">
+      <c r="B24" s="14">
         <v>4</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15">
         <v>2</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18">
+      <c r="E24" s="17"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15">
         <v>1</v>
       </c>
-      <c r="I24" s="19"/>
+      <c r="I24" s="17"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
@@ -5423,14 +6177,14 @@
       <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="23"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="25"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="33"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
@@ -5440,20 +6194,20 @@
       <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="26">
+      <c r="B26" s="12">
         <v>1</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="26">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16">
+      <c r="G26" s="13"/>
+      <c r="H26" s="13">
         <v>4</v>
       </c>
-      <c r="I26" s="17"/>
+      <c r="I26" s="16"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35"/>
@@ -5463,14 +6217,14 @@
       <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="19"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="17"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="35"/>
@@ -5480,14 +6234,14 @@
       <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="22"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="19"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="17"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
       <c r="M28" s="35"/>
@@ -5497,17 +6251,22 @@
       <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="25"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -5522,18 +6281,13 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFAF56D-3771-45EA-B0C5-14F1F62B7279}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -6384,32 +7138,32 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="26">
+      <c r="B22" s="12">
         <v>3</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13">
         <v>1</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="27">
+      <c r="E22" s="16"/>
+      <c r="F22" s="18">
         <v>4</v>
       </c>
-      <c r="G22" s="28"/>
-      <c r="H22" s="16">
+      <c r="G22" s="19"/>
+      <c r="H22" s="13">
         <v>2</v>
       </c>
-      <c r="I22" s="17"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="19"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="17"/>
       <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
@@ -6421,22 +7175,22 @@
       <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="B24" s="22">
         <v>4</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15">
+      <c r="C24" s="23"/>
+      <c r="D24" s="23">
         <v>2</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22">
+      <c r="E24" s="26"/>
+      <c r="F24" s="14">
         <v>3</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="15">
+      <c r="G24" s="15"/>
+      <c r="H24" s="23">
         <v>1</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="26"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
@@ -6446,14 +7200,14 @@
       <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="31"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="27"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
@@ -6463,22 +7217,22 @@
       <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
+      <c r="B26" s="30">
         <v>1</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="16">
+      <c r="C26" s="31"/>
+      <c r="D26" s="13">
         <v>3</v>
       </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="12">
+      <c r="E26" s="16"/>
+      <c r="F26" s="30">
         <v>2</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13">
+      <c r="G26" s="31"/>
+      <c r="H26" s="31">
         <v>4</v>
       </c>
-      <c r="I26" s="20"/>
+      <c r="I26" s="32"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35"/>
@@ -6488,14 +7242,14 @@
       <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="21"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="26"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="35"/>
@@ -6505,22 +7259,22 @@
       <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="22">
+      <c r="B28" s="14">
         <v>2</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15">
         <v>4</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="22">
+      <c r="E28" s="17"/>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18">
+      <c r="G28" s="15"/>
+      <c r="H28" s="15">
         <v>3</v>
       </c>
-      <c r="I28" s="19"/>
+      <c r="I28" s="17"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
       <c r="M28" s="35"/>
@@ -6530,14 +7284,14 @@
       <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="25"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="33"/>
       <c r="K29" s="36" t="s">
         <v>58</v>
       </c>
@@ -6565,6 +7319,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K29:P31"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I29"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="D20:P21"/>
     <mergeCell ref="B22:C23"/>
@@ -6575,16 +7339,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:E25"/>
     <mergeCell ref="F24:G25"/>
-    <mergeCell ref="K29:P31"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="F28:G29"/>
-    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6592,7 +7346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D81932-AA73-47DC-82CB-EC0E532772F7}">
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ottawa_Visuals\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB41CFF-20F5-4CBA-B6E9-3D56D7A9A597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA62962-B6E4-483F-AF49-6C5DE80654BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adventure Tracker" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="181">
   <si>
     <t>Line/Column</t>
   </si>
@@ -438,9 +438,6 @@
   </si>
   <si>
     <t>🎒 Backpack Adventure – Master Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🟦 Items needed now (used at this stage)     🟨 Items received early but used later     🟩 Solution logic     🟧 Code / Answer     🟪 Unlocks</t>
   </si>
   <si>
     <t>── LOCATION ──</t>
@@ -497,9 +494,6 @@
 (1–5)</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -529,9 +523,6 @@
   </si>
   <si>
     <t>Front Compartment</t>
-  </si>
-  <si>
-    <t>✅ Done</t>
   </si>
   <si>
     <t>Front zip
@@ -638,7 +629,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,12 +699,6 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
       <sz val="8"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
@@ -765,7 +750,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,11 +783,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2C3E6B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F4FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1030,7 +1010,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1055,22 +1035,133 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1085,40 +1176,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1129,94 +1193,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1901,8 +1877,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF98571C-67F3-4A93-A173-F5ACBB578192}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1914,324 +1890,290 @@
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-    </row>
-    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+    </row>
+    <row r="2" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40" t="s">
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-    </row>
-    <row r="4" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="B3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="C3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="D3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="E3" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F3" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="G3" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="H3" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="I3" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="J3" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="K3" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="L3" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="L4" s="41" t="s">
+    </row>
+    <row r="4" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="19">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="C4" s="21" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
-        <v>1</v>
-      </c>
-      <c r="B5" s="48" t="s">
+      <c r="D4" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="E4" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="F4" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="H4" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="49" t="s">
+      <c r="I4" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="J4" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="I5" s="53" t="s">
+      <c r="K4" s="27">
+        <v>3</v>
+      </c>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29">
+        <v>2</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="D5" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="55">
+      <c r="F5" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="K5" s="33">
         <v>3</v>
       </c>
-      <c r="L5" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="M5" s="56"/>
-    </row>
-    <row r="6" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57">
+      <c r="L5" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="19">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="K6" s="27">
         <v>2</v>
       </c>
-      <c r="B6" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="J6" s="54" t="s">
-        <v>165</v>
-      </c>
-      <c r="K6" s="61">
-        <v>3</v>
-      </c>
-      <c r="L6" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="M6" s="62" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
-        <v>3</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="49" t="s">
+      <c r="L6" s="28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="29">
+        <v>4</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H7" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="I7" s="53" t="s">
+      <c r="C7" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="54" t="s">
+      <c r="D7" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="K7" s="55">
-        <v>2</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="M7" s="56" t="s">
+      <c r="E7" s="22" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57">
+      <c r="F7" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="33">
         <v>4</v>
       </c>
-      <c r="B8" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="59" t="s">
-        <v>179</v>
-      </c>
-      <c r="H8" s="52" t="s">
+      <c r="L7" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="J8" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="K8" s="61">
-        <v>4</v>
-      </c>
-      <c r="L8" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="M8" s="62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="63">
+    </row>
+    <row r="8" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="35">
         <v>5</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="59"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="K5:K9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="K4:K8" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
       <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L5:L9" xr:uid="{4D7E9BDF-04E7-4D7D-A558-7BBC5E7910BC}">
-      <formula1>"🔲 Not Started,🔧 In Progress,✅ Done,⏸ On Hold"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBB895D-374E-47E9-B67F-28D3C51CD256}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D260E2E-9366-4C07-AD85-6CF609B51D36}">
   <dimension ref="A2:M17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2239,7 +2181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2247,7 +2189,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -2255,7 +2197,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>116</v>
       </c>
@@ -2266,7 +2208,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>118</v>
       </c>
@@ -2277,7 +2219,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>119</v>
       </c>
@@ -2288,12 +2230,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -2335,7 +2277,7 @@
         <v>25.830000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>123</v>
       </c>
@@ -2374,7 +2316,7 @@
         <v>41.92</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C16">
         <f>C14-C9/10</f>
         <v>20.96</v>
@@ -2384,7 +2326,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C17">
         <f>C13-(C8+C10)/10</f>
         <v>11.93</v>
@@ -2395,6 +2337,9 @@
     <hyperlink ref="C7" r:id="rId1" xr:uid="{9720C1EA-3CA5-4BDB-9AD5-468174E727DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2404,18 +2349,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:AU39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="3.28515625" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="19" max="38" width="3.28515625" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="16.42578125" customWidth="1"/>
-    <col min="46" max="46" width="14.85546875" customWidth="1"/>
-    <col min="47" max="47" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="3.26953125" customWidth="1"/>
+    <col min="18" max="18" width="12.453125" hidden="1" customWidth="1"/>
+    <col min="19" max="38" width="3.26953125" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="16.453125" customWidth="1"/>
+    <col min="46" max="46" width="14.81640625" customWidth="1"/>
+    <col min="47" max="47" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2534,7 +2479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2588,83 +2533,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB2" s="1">
+      <c r="AI2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
       <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -2677,7 +2622,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2731,83 +2676,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>2</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="T3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="W3" s="1">
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AE3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Z3" s="1">
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AJ3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
       <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2822,7 +2767,7 @@
         <v>401926.91000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2876,83 +2821,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="V4" s="1">
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="X4" s="1">
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>26</v>
       </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG4" s="1">
+      <c r="AK4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2971,7 +2916,7 @@
         <v>59.290000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3029,79 +2974,79 @@
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="X5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y5" s="1">
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AH5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -3120,7 +3065,7 @@
         <v>401926.91000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3174,83 +3119,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="V6" s="1">
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AH6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH6" s="1">
+      <c r="AK6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AK6" s="1">
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -3260,7 +3205,7 @@
       </c>
       <c r="AS6" s="7"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3314,83 +3259,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="U7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="V7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="W7" s="1">
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AD7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD7" s="1">
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AH7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
       <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AJ7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -3407,7 +3352,7 @@
         <v>6779</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3461,83 +3406,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="T8" s="1">
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="U8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AG8" s="1">
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AJ8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
       <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -3547,7 +3492,7 @@
       </c>
       <c r="AS8" s="7"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3601,83 +3546,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AJ9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AK9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AL9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
-      </c>
-      <c r="U9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -3693,7 +3638,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3747,83 +3692,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
       <c r="V10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE10" s="1">
+      <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3832,7 +3777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3886,83 +3831,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="V11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="X11" s="1">
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AJ11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ11" s="1">
+      <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -3974,7 +3919,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4028,83 +3973,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="T12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="V12" s="1">
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -4113,7 +4058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4167,83 +4112,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="T13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="U13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
       <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -4256,7 +4201,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4310,83 +4255,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB14" s="1">
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
       <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -4395,7 +4340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4449,83 +4394,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -4534,7 +4479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4588,83 +4533,83 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -4680,7 +4625,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4725,7 +4670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>5</v>
@@ -4790,7 +4735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -4866,7 +4811,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -4932,7 +4877,7 @@
         <v>401926.91</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4988,7 +4933,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
       <c r="O22" s="1" t="s">
         <v>41</v>
       </c>
@@ -5008,7 +4953,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>20</v>
       </c>
@@ -5043,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -5085,7 +5030,7 @@
         <v>6778.9999999999991</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
       <c r="O25" s="1" t="s">
         <v>31</v>
       </c>
@@ -5106,7 +5051,7 @@
         <v>407.99999999999909</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
       <c r="L26" t="s">
         <v>50</v>
       </c>
@@ -5132,126 +5077,134 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="12">
+    <row r="28" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="C29" s="54">
         <v>3</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13">
+      <c r="D29" s="44"/>
+      <c r="E29" s="44">
         <v>1</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="18">
+      <c r="F29" s="45"/>
+      <c r="G29" s="55">
         <v>4</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="13">
+      <c r="H29" s="56"/>
+      <c r="I29" s="44">
         <v>2</v>
       </c>
-      <c r="J29" s="16"/>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="22">
+      <c r="J29" s="45"/>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="C30" s="50"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="47"/>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="C31" s="42">
         <v>4</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23">
+      <c r="D31" s="43"/>
+      <c r="E31" s="43">
         <v>2</v>
       </c>
-      <c r="F31" s="26"/>
-      <c r="G31" s="14">
+      <c r="F31" s="49"/>
+      <c r="G31" s="50">
         <v>3</v>
       </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="23">
+      <c r="H31" s="46"/>
+      <c r="I31" s="43">
         <v>1</v>
       </c>
-      <c r="J31" s="26"/>
-    </row>
-    <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="27"/>
-    </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="30">
+      <c r="J31" s="49"/>
+    </row>
+    <row r="32" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="59"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61"/>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C33" s="40">
         <v>1</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="13">
+      <c r="D33" s="41"/>
+      <c r="E33" s="44">
         <v>3</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="30">
+      <c r="F33" s="45"/>
+      <c r="G33" s="40">
         <v>2</v>
       </c>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31">
+      <c r="H33" s="41"/>
+      <c r="I33" s="41">
         <v>4</v>
       </c>
-      <c r="J33" s="32"/>
-    </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="22"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="14">
+      <c r="J33" s="48"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C34" s="42"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="49"/>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C35" s="50">
         <v>2</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15">
+      <c r="D35" s="46"/>
+      <c r="E35" s="46">
         <v>4</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="14">
+      <c r="F35" s="47"/>
+      <c r="G35" s="50">
         <v>1</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15">
+      <c r="H35" s="46"/>
+      <c r="I35" s="46">
         <v>3</v>
       </c>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="33"/>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="47"/>
+    </row>
+    <row r="36" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="53"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.35">
       <c r="F39" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:F34"/>
     <mergeCell ref="G33:H34"/>
@@ -5260,16 +5213,11 @@
     <mergeCell ref="E35:F36"/>
     <mergeCell ref="G35:H36"/>
     <mergeCell ref="I35:J36"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -5279,46 +5227,46 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:Q29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="17" width="3.28515625" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" customWidth="1"/>
+    <col min="2" max="17" width="3.26953125" customWidth="1"/>
+    <col min="18" max="18" width="3.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="34" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D2" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -5368,7 +5316,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>35</v>
       </c>
@@ -5418,7 +5366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
@@ -5468,7 +5416,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
@@ -5518,7 +5466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>41</v>
       </c>
@@ -5568,7 +5516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
@@ -5618,7 +5566,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
@@ -5668,7 +5616,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -5718,7 +5666,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
@@ -5768,7 +5716,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
@@ -5818,7 +5766,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
@@ -5868,7 +5816,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
@@ -5918,7 +5866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
@@ -5968,7 +5916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -6018,7 +5966,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
@@ -6068,7 +6016,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -6086,187 +6034,182 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="16"/>
-    </row>
-    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
-      <c r="K23" s="35" t="s">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B22" s="54"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="50"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="K23" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="63"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B24" s="50">
         <v>4</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15">
+      <c r="C24" s="46"/>
+      <c r="D24" s="46">
         <v>2</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15">
+      <c r="E24" s="47"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46">
         <v>1</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="33"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
+      <c r="I24" s="47"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+    </row>
+    <row r="25" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="53"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="63"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B26" s="54">
         <v>1</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="12">
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="54">
         <v>2</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13">
+      <c r="G26" s="44"/>
+      <c r="H26" s="44">
         <v>4</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="17"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="17"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
+      <c r="I26" s="45"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="63"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B27" s="50"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B28" s="50"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="47"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="63"/>
+    </row>
+    <row r="29" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -6281,9 +6224,17 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6293,45 +6244,45 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:Q31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="17" width="3.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" customWidth="1"/>
+    <col min="2" max="17" width="3.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="34" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D2" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -6381,7 +6332,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>35</v>
       </c>
@@ -6431,7 +6382,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
@@ -6481,7 +6432,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
@@ -6531,7 +6482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>41</v>
       </c>
@@ -6581,7 +6532,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
@@ -6631,7 +6582,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
@@ -6681,7 +6632,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -6731,7 +6682,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
@@ -6781,7 +6732,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
@@ -6831,7 +6782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
@@ -6881,7 +6832,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
@@ -6931,7 +6882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
@@ -6981,7 +6932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -7031,7 +6982,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
@@ -7081,7 +7032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -7099,226 +7050,236 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="12">
+    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="54">
         <v>3</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13">
+      <c r="C22" s="44"/>
+      <c r="D22" s="44">
         <v>1</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18">
+      <c r="E22" s="45"/>
+      <c r="F22" s="55">
         <v>4</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13">
+      <c r="G22" s="56"/>
+      <c r="H22" s="44">
         <v>2</v>
       </c>
-      <c r="I22" s="16"/>
-    </row>
-    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
-      <c r="K23" s="35" t="s">
+      <c r="I22" s="45"/>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="50"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="K23" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-    </row>
-    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22">
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="63"/>
+    </row>
+    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="42">
         <v>4</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23">
+      <c r="C24" s="43"/>
+      <c r="D24" s="43">
         <v>2</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="14">
+      <c r="E24" s="49"/>
+      <c r="F24" s="50">
         <v>3</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="23">
+      <c r="G24" s="46"/>
+      <c r="H24" s="43">
         <v>1</v>
       </c>
-      <c r="I24" s="26"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="27"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-    </row>
-    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30">
+      <c r="I24" s="49"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+    </row>
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="63"/>
+    </row>
+    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="40">
         <v>1</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="13">
+      <c r="C26" s="41"/>
+      <c r="D26" s="44">
         <v>3</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="30">
+      <c r="E26" s="45"/>
+      <c r="F26" s="40">
         <v>2</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31">
+      <c r="G26" s="41"/>
+      <c r="H26" s="41">
         <v>4</v>
       </c>
-      <c r="I26" s="32"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-    </row>
-    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="26"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-    </row>
-    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+      <c r="I26" s="48"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="63"/>
+    </row>
+    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="49"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+    </row>
+    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="50">
         <v>2</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15">
+      <c r="C28" s="46"/>
+      <c r="D28" s="46">
         <v>4</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14">
+      <c r="E28" s="47"/>
+      <c r="F28" s="50">
         <v>1</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15">
+      <c r="G28" s="46"/>
+      <c r="H28" s="46">
         <v>3</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
-      <c r="K29" s="36" t="s">
+      <c r="I28" s="47"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="63"/>
+    </row>
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="53"/>
+      <c r="K29" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="36"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="P30" s="36"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-      <c r="P31" s="36"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="F24:G25"/>
     <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
     <mergeCell ref="B26:C27"/>
@@ -7329,19 +7290,12 @@
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="F24:G25"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7349,12 +7303,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D81932-AA73-47DC-82CB-EC0E532772F7}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="6" width="15.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
@@ -7374,7 +7328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
@@ -7394,7 +7348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -7414,7 +7368,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>67</v>
       </c>
@@ -7434,7 +7388,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>68</v>
       </c>
@@ -7454,7 +7408,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
@@ -7474,87 +7428,96 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{219619fd-75dc-48cb-820d-8f683a95dd8b}" enabled="1" method="Privileged" siteId="{05c95b33-90ca-49d5-b644-288b930b912b}" contentBits="1" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ottawa_Visuals\EscapeBackpack\Hiking_Trip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA62962-B6E4-483F-AF49-6C5DE80654BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71A6B75-A2F7-4CB0-9B38-474F762F9ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adventure Tracker" sheetId="7" r:id="rId1"/>
@@ -1119,49 +1119,22 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1176,13 +1149,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1878,7 +1878,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF98571C-67F3-4A93-A173-F5ACBB578192}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1893,7 +1893,7 @@
     <col min="12" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>131</v>
       </c>
@@ -1909,7 +1909,7 @@
       <c r="K1" s="39"/>
       <c r="L1" s="39"/>
     </row>
-    <row r="2" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12" t="s">
@@ -1931,7 +1931,7 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>136</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L4" s="28"/>
     </row>
-    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <v>2</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>3</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>4</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>5</v>
       </c>
@@ -2154,7 +2154,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBB895D-374E-47E9-B67F-28D3C51CD256}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2166,14 +2166,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D260E2E-9366-4C07-AD85-6CF609B51D36}">
   <dimension ref="A2:M17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>116</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>118</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>119</v>
       </c>
@@ -2230,12 +2230,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>25.830000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>123</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>41.92</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C16">
         <f>C14-C9/10</f>
         <v>20.96</v>
@@ -2326,7 +2326,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17">
         <f>C13-(C8+C10)/10</f>
         <v>11.93</v>
@@ -2349,18 +2349,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:AU39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="3.26953125" customWidth="1"/>
-    <col min="18" max="18" width="12.453125" hidden="1" customWidth="1"/>
-    <col min="19" max="38" width="3.26953125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="16.453125" customWidth="1"/>
-    <col min="46" max="46" width="14.81640625" customWidth="1"/>
-    <col min="47" max="47" width="18.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="3.28515625" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="19" max="38" width="3.28515625" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="16.42578125" customWidth="1"/>
+    <col min="46" max="46" width="14.85546875" customWidth="1"/>
+    <col min="47" max="47" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2533,79 +2533,79 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>14</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="U2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="AK2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -2622,7 +2622,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2676,83 +2676,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>3</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="T3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="V3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
       <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>401926.91000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2821,83 +2821,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AK4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AL4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
-      </c>
-      <c r="T4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2916,7 +2916,7 @@
         <v>59.290000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2970,83 +2970,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="T5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="U5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="V5" s="1">
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AA5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="W5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X5" s="1">
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AC5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="Y5" s="1">
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="Z5" s="1">
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AI5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB5" s="1">
+      <c r="AJ5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -3065,7 +3065,7 @@
         <v>401926.91000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3119,83 +3119,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="T6" s="1">
+      <c r="AD6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="U6" s="1">
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AJ6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="V6" s="1">
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AS6" s="7"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3259,83 +3259,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="T7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AF7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="V7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AC7" s="1">
+      <c r="AG7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
       <c r="AH7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -3352,7 +3352,7 @@
         <v>6779</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3414,75 +3414,75 @@
       </c>
       <c r="U8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="W8" s="1">
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AJ8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AF8" s="1">
+      <c r="AK8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AL8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AS8" s="7"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3546,83 +3546,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="U9" s="1">
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AD9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Y9" s="1">
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AF9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AA9" s="1">
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AH9" s="1">
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AJ9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -3638,7 +3638,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3692,83 +3692,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="U10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="V10" s="1">
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z10" s="1">
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AG10" s="1">
+      <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3777,7 +3777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3831,83 +3831,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="T11" s="1">
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AF11" s="1">
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -3919,7 +3919,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3973,83 +3973,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="T12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="V12" s="1">
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AJ12" s="1">
+      <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AL12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -4058,7 +4058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4112,83 +4112,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AA13" s="1">
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AE13" s="1">
+      <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -4201,7 +4201,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4255,83 +4255,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="X14" s="1">
+      <c r="AG14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE14" s="1">
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AI14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AG14" s="1">
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AK14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -4340,7 +4340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4394,63 +4394,63 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="U15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="V15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -4458,19 +4458,19 @@
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4533,83 +4533,83 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -4625,7 +4625,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4670,7 +4670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>5</v>
@@ -4735,7 +4735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -4811,7 +4811,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -4877,7 +4877,7 @@
         <v>401926.91</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4933,7 +4933,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="O22" s="1" t="s">
         <v>41</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>20</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>6778.9999999999991</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="O25" s="1" t="s">
         <v>31</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>407.99999999999909</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="L26" t="s">
         <v>50</v>
       </c>
@@ -5077,126 +5077,134 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="C29" s="54">
+    <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="C29" s="40">
         <v>3</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44">
+      <c r="D29" s="41"/>
+      <c r="E29" s="41">
         <v>1</v>
       </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="55">
+      <c r="F29" s="44"/>
+      <c r="G29" s="46">
         <v>4</v>
       </c>
-      <c r="H29" s="56"/>
-      <c r="I29" s="44">
+      <c r="H29" s="47"/>
+      <c r="I29" s="41">
         <v>2</v>
       </c>
-      <c r="J29" s="45"/>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="C30" s="50"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="47"/>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="C31" s="42">
+      <c r="J29" s="44"/>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="C30" s="42"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="45"/>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="C31" s="50">
         <v>4</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43">
+      <c r="D31" s="51"/>
+      <c r="E31" s="51">
         <v>2</v>
       </c>
-      <c r="F31" s="49"/>
-      <c r="G31" s="50">
+      <c r="F31" s="54"/>
+      <c r="G31" s="42">
         <v>3</v>
       </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="43">
+      <c r="H31" s="43"/>
+      <c r="I31" s="51">
         <v>1</v>
       </c>
-      <c r="J31" s="49"/>
-    </row>
-    <row r="32" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C32" s="59"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="61"/>
-    </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C33" s="40">
+      <c r="J31" s="54"/>
+    </row>
+    <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="52"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="55"/>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C33" s="58">
         <v>1</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="44">
+      <c r="D33" s="59"/>
+      <c r="E33" s="41">
         <v>3</v>
       </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="40">
+      <c r="F33" s="44"/>
+      <c r="G33" s="58">
         <v>2</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41">
+      <c r="H33" s="59"/>
+      <c r="I33" s="59">
         <v>4</v>
       </c>
-      <c r="J33" s="48"/>
-    </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C34" s="42"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="49"/>
-    </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C35" s="50">
+      <c r="J33" s="60"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="54"/>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C35" s="42">
         <v>2</v>
       </c>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46">
+      <c r="D35" s="43"/>
+      <c r="E35" s="43">
         <v>4</v>
       </c>
-      <c r="F35" s="47"/>
-      <c r="G35" s="50">
+      <c r="F35" s="45"/>
+      <c r="G35" s="42">
         <v>1</v>
       </c>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46">
+      <c r="H35" s="43"/>
+      <c r="I35" s="43">
         <v>3</v>
       </c>
-      <c r="J35" s="47"/>
-    </row>
-    <row r="36" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C36" s="51"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="53"/>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="56"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="61"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
     <mergeCell ref="C29:D30"/>
     <mergeCell ref="E29:F30"/>
     <mergeCell ref="G29:H30"/>
@@ -5205,14 +5213,6 @@
     <mergeCell ref="E31:F32"/>
     <mergeCell ref="G31:H32"/>
     <mergeCell ref="I31:J32"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5227,14 +5227,14 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:Q29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" customWidth="1"/>
-    <col min="2" max="17" width="3.26953125" customWidth="1"/>
-    <col min="18" max="18" width="3.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="17" width="3.28515625" customWidth="1"/>
+    <col min="18" max="18" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D2" s="62" t="s">
         <v>54</v>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
@@ -5266,7 +5266,7 @@
       <c r="O3" s="62"/>
       <c r="P3" s="62"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -5313,10 +5313,10 @@
         <v>41</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>35</v>
       </c>
@@ -5363,10 +5363,10 @@
         <v>36</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
@@ -5413,10 +5413,10 @@
         <v>34</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
@@ -5463,10 +5463,10 @@
         <v>46</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>41</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
@@ -5563,10 +5563,10 @@
         <v>51</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
@@ -5613,10 +5613,10 @@
         <v>36</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -5663,10 +5663,10 @@
         <v>32</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
@@ -5713,10 +5713,10 @@
         <v>47</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
@@ -5763,10 +5763,10 @@
         <v>40</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
@@ -5813,10 +5813,10 @@
         <v>42</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
@@ -5863,10 +5863,10 @@
         <v>35</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
@@ -5913,10 +5913,10 @@
         <v>31</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -5963,10 +5963,10 @@
         <v>44</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
@@ -6013,10 +6013,10 @@
         <v>46</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -6034,7 +6034,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="62" t="s">
@@ -6054,7 +6054,7 @@
       <c r="P20" s="62"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="62"/>
@@ -6072,25 +6072,25 @@
       <c r="P21" s="62"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B22" s="54"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-    </row>
-    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="50"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="44"/>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="45"/>
       <c r="K23" s="63" t="s">
         <v>56</v>
       </c>
@@ -6101,21 +6101,21 @@
       <c r="P23" s="63"/>
       <c r="Q23" s="63"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B24" s="50">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24" s="42">
         <v>4</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46">
+      <c r="C24" s="43"/>
+      <c r="D24" s="43">
         <v>2</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46">
+      <c r="E24" s="45"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43">
         <v>1</v>
       </c>
-      <c r="I24" s="47"/>
+      <c r="I24" s="45"/>
       <c r="K24" s="63"/>
       <c r="L24" s="63"/>
       <c r="M24" s="63"/>
@@ -6124,15 +6124,15 @@
       <c r="P24" s="63"/>
       <c r="Q24" s="63"/>
     </row>
-    <row r="25" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="53"/>
+    <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="61"/>
       <c r="K25" s="63"/>
       <c r="L25" s="63"/>
       <c r="M25" s="63"/>
@@ -6141,21 +6141,21 @@
       <c r="P25" s="63"/>
       <c r="Q25" s="63"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B26" s="54">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="40">
         <v>1</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="54">
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="40">
         <v>2</v>
       </c>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44">
+      <c r="G26" s="41"/>
+      <c r="H26" s="41">
         <v>4</v>
       </c>
-      <c r="I26" s="45"/>
+      <c r="I26" s="44"/>
       <c r="K26" s="63"/>
       <c r="L26" s="63"/>
       <c r="M26" s="63"/>
@@ -6164,15 +6164,15 @@
       <c r="P26" s="63"/>
       <c r="Q26" s="63"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B27" s="50"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="45"/>
       <c r="K27" s="63"/>
       <c r="L27" s="63"/>
       <c r="M27" s="63"/>
@@ -6181,15 +6181,15 @@
       <c r="P27" s="63"/>
       <c r="Q27" s="63"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B28" s="50"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="47"/>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="42"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="45"/>
       <c r="K28" s="63"/>
       <c r="L28" s="63"/>
       <c r="M28" s="63"/>
@@ -6198,18 +6198,23 @@
       <c r="P28" s="63"/>
       <c r="Q28" s="63"/>
     </row>
-    <row r="29" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
+    <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="56"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -6224,11 +6229,6 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6244,13 +6244,13 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:Q31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" customWidth="1"/>
-    <col min="2" max="17" width="3.26953125" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="17" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D2" s="62" t="s">
         <v>54</v>
       </c>
@@ -6267,7 +6267,7 @@
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
@@ -6282,7 +6282,7 @@
       <c r="O3" s="62"/>
       <c r="P3" s="62"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>35</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>41</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -7050,7 +7050,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="62" t="s">
@@ -7070,7 +7070,7 @@
       <c r="P20" s="62"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="62"/>
@@ -7088,33 +7088,33 @@
       <c r="P21" s="62"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="54">
+    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="40">
         <v>3</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44">
+      <c r="C22" s="41"/>
+      <c r="D22" s="41">
         <v>1</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="55">
+      <c r="E22" s="44"/>
+      <c r="F22" s="46">
         <v>4</v>
       </c>
-      <c r="G22" s="56"/>
-      <c r="H22" s="44">
+      <c r="G22" s="47"/>
+      <c r="H22" s="41">
         <v>2</v>
       </c>
-      <c r="I22" s="45"/>
-    </row>
-    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="50"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
+      <c r="I22" s="44"/>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="45"/>
       <c r="K23" s="63" t="s">
         <v>56</v>
       </c>
@@ -7125,23 +7125,23 @@
       <c r="P23" s="63"/>
       <c r="Q23" s="63"/>
     </row>
-    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="42">
+    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="50">
         <v>4</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43">
+      <c r="C24" s="51"/>
+      <c r="D24" s="51">
         <v>2</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50">
+      <c r="E24" s="54"/>
+      <c r="F24" s="42">
         <v>3</v>
       </c>
-      <c r="G24" s="46"/>
-      <c r="H24" s="43">
+      <c r="G24" s="43"/>
+      <c r="H24" s="51">
         <v>1</v>
       </c>
-      <c r="I24" s="49"/>
+      <c r="I24" s="54"/>
       <c r="K24" s="63"/>
       <c r="L24" s="63"/>
       <c r="M24" s="63"/>
@@ -7150,15 +7150,15 @@
       <c r="P24" s="63"/>
       <c r="Q24" s="63"/>
     </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="59"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="61"/>
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="52"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="55"/>
       <c r="K25" s="63"/>
       <c r="L25" s="63"/>
       <c r="M25" s="63"/>
@@ -7167,23 +7167,23 @@
       <c r="P25" s="63"/>
       <c r="Q25" s="63"/>
     </row>
-    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="40">
+    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="58">
         <v>1</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="44">
+      <c r="C26" s="59"/>
+      <c r="D26" s="41">
         <v>3</v>
       </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="40">
+      <c r="E26" s="44"/>
+      <c r="F26" s="58">
         <v>2</v>
       </c>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41">
+      <c r="G26" s="59"/>
+      <c r="H26" s="59">
         <v>4</v>
       </c>
-      <c r="I26" s="48"/>
+      <c r="I26" s="60"/>
       <c r="K26" s="63"/>
       <c r="L26" s="63"/>
       <c r="M26" s="63"/>
@@ -7192,15 +7192,15 @@
       <c r="P26" s="63"/>
       <c r="Q26" s="63"/>
     </row>
-    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="49"/>
+    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="50"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="54"/>
       <c r="K27" s="63"/>
       <c r="L27" s="63"/>
       <c r="M27" s="63"/>
@@ -7209,23 +7209,23 @@
       <c r="P27" s="63"/>
       <c r="Q27" s="63"/>
     </row>
-    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="50">
+    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="42">
         <v>2</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46">
+      <c r="C28" s="43"/>
+      <c r="D28" s="43">
         <v>4</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="50">
+      <c r="E28" s="45"/>
+      <c r="F28" s="42">
         <v>1</v>
       </c>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46">
+      <c r="G28" s="43"/>
+      <c r="H28" s="43">
         <v>3</v>
       </c>
-      <c r="I28" s="47"/>
+      <c r="I28" s="45"/>
       <c r="K28" s="63"/>
       <c r="L28" s="63"/>
       <c r="M28" s="63"/>
@@ -7234,15 +7234,15 @@
       <c r="P28" s="63"/>
       <c r="Q28" s="63"/>
     </row>
-    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="56"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="61"/>
       <c r="K29" s="64" t="s">
         <v>58</v>
       </c>
@@ -7252,7 +7252,7 @@
       <c r="O29" s="64"/>
       <c r="P29" s="64"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="K30" s="64"/>
       <c r="L30" s="64"/>
       <c r="M30" s="64"/>
@@ -7260,7 +7260,7 @@
       <c r="O30" s="64"/>
       <c r="P30" s="64"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="K31" s="64"/>
       <c r="L31" s="64"/>
       <c r="M31" s="64"/>
@@ -7270,6 +7270,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K29:P31"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I29"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="D20:P21"/>
     <mergeCell ref="B22:C23"/>
@@ -7280,16 +7290,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:E25"/>
     <mergeCell ref="F24:G25"/>
-    <mergeCell ref="K29:P31"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="F28:G29"/>
-    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -7303,12 +7303,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D81932-AA73-47DC-82CB-EC0E532772F7}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="15.7265625" style="1" customWidth="1"/>
+    <col min="1" max="6" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>67</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>68</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
@@ -7428,82 +7428,82 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>109</v>
       </c>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71A6B75-A2F7-4CB0-9B38-474F762F9ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB089E-65C7-4226-958F-D9BDA2871FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adventure Tracker" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="185">
   <si>
     <t>Line/Column</t>
   </si>
@@ -619,6 +619,18 @@
   </si>
   <si>
     <t>Hardest stage — player must use items collected in stages 2 &amp; 3</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Main Handle</t>
+  </si>
+  <si>
+    <t>Escape Backpack QR code card</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1128,22 @@
     <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1125,16 +1152,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1149,10 +1170,28 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1161,35 +1200,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1877,12 +1889,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF98571C-67F3-4A93-A173-F5ACBB578192}">
-  <dimension ref="A1:L8"/>
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
@@ -1894,20 +1909,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
@@ -1969,178 +1984,212 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
+        <v>0</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="27"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B5" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C5" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D5" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F5" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G5" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H5" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I5" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J5" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K5" s="27">
         <v>3</v>
       </c>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29">
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29">
         <v>2</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B6" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C6" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D6" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F6" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G6" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H6" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I6" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J6" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K6" s="33">
         <v>3</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L6" s="34" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B7" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C7" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D7" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F7" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G7" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H7" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I7" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J7" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K7" s="27">
         <v>2</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L7" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+    <row r="8" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29">
         <v>4</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B8" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C8" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D8" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F8" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G8" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H8" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I8" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J8" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K8" s="33">
         <v>4</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="L8" s="34" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+    <row r="9" spans="1:12" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="35">
         <v>5</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K4:K8" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
+    <dataValidation type="list" allowBlank="1" sqref="K5:K9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2533,83 +2582,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>1</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="U2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="V2" s="1">
+      <c r="AJ2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -2676,83 +2725,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>18</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="T3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V3" s="1">
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
       <c r="AC3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AD3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AK3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AL3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>24</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2821,83 +2870,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AK4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
       <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -2970,7 +3019,7 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -2978,27 +3027,27 @@
       </c>
       <c r="U5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Y5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Z5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA5" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3006,47 +3055,47 @@
       </c>
       <c r="AB5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
       <c r="AE5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AF5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AH5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AJ5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -3119,83 +3168,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="U6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Z6" s="1">
+      <c r="AI6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AC6" s="1">
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -3259,83 +3308,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="U7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="V7" s="1">
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AH7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AI7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC7" s="1">
+      <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AJ7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -3406,83 +3455,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
       <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -3546,83 +3595,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="T9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="U9" s="1">
+      <c r="Z9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="V9" s="1">
+      <c r="AA9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AG9" s="1">
+      <c r="AK9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -3692,83 +3741,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="U10" s="1">
+      <c r="AK10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3831,79 +3880,79 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="V11" s="1">
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AJ11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
       <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3977,75 +4026,75 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
       <c r="Y12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE12" s="1">
+      <c r="AF12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AG12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AI12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4112,83 +4161,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA13" s="1">
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AC13" s="1">
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -4255,83 +4304,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="T14" s="1">
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>26</v>
       </c>
-      <c r="U14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="V14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AB14" s="1">
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AE14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
       <c r="AF14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ14" s="1">
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -4394,39 +4443,39 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="T15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="U15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="V15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Z15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
@@ -4434,43 +4483,43 @@
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -4533,83 +4582,83 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -5079,116 +5128,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="40">
+      <c r="C29" s="45">
         <v>3</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41">
+      <c r="D29" s="46"/>
+      <c r="E29" s="46">
         <v>1</v>
       </c>
-      <c r="F29" s="44"/>
-      <c r="G29" s="46">
+      <c r="F29" s="48"/>
+      <c r="G29" s="49">
         <v>4</v>
       </c>
-      <c r="H29" s="47"/>
-      <c r="I29" s="41">
+      <c r="H29" s="50"/>
+      <c r="I29" s="46">
         <v>2</v>
       </c>
-      <c r="J29" s="44"/>
+      <c r="J29" s="48"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="45"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="43"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="50">
+      <c r="C31" s="57">
         <v>4</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51">
+      <c r="D31" s="58"/>
+      <c r="E31" s="58">
         <v>2</v>
       </c>
-      <c r="F31" s="54"/>
-      <c r="G31" s="42">
+      <c r="F31" s="60"/>
+      <c r="G31" s="39">
         <v>3</v>
       </c>
-      <c r="H31" s="43"/>
-      <c r="I31" s="51">
+      <c r="H31" s="40"/>
+      <c r="I31" s="58">
         <v>1</v>
       </c>
-      <c r="J31" s="54"/>
+      <c r="J31" s="60"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="52"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="55"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="63"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="58">
+      <c r="C33" s="55">
         <v>1</v>
       </c>
-      <c r="D33" s="59"/>
-      <c r="E33" s="41">
+      <c r="D33" s="56"/>
+      <c r="E33" s="46">
         <v>3</v>
       </c>
-      <c r="F33" s="44"/>
-      <c r="G33" s="58">
+      <c r="F33" s="48"/>
+      <c r="G33" s="55">
         <v>2</v>
       </c>
-      <c r="H33" s="59"/>
-      <c r="I33" s="59">
+      <c r="H33" s="56"/>
+      <c r="I33" s="56">
         <v>4</v>
       </c>
-      <c r="J33" s="60"/>
+      <c r="J33" s="59"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="50"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="54"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="60"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="42">
+      <c r="C35" s="39">
         <v>2</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43">
+      <c r="D35" s="40"/>
+      <c r="E35" s="40">
         <v>4</v>
       </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="42">
+      <c r="F35" s="43"/>
+      <c r="G35" s="39">
         <v>1</v>
       </c>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43">
+      <c r="H35" s="40"/>
+      <c r="I35" s="40">
         <v>3</v>
       </c>
-      <c r="J35" s="45"/>
+      <c r="J35" s="43"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="56"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="61"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -5197,6 +5246,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:F34"/>
     <mergeCell ref="G33:H34"/>
@@ -5205,14 +5262,6 @@
     <mergeCell ref="E35:F36"/>
     <mergeCell ref="G35:H36"/>
     <mergeCell ref="I35:J36"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5235,36 +5284,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -6037,184 +6086,179 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="62" t="s">
+      <c r="D20" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="45"/>
-      <c r="K23" s="63" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="43"/>
+      <c r="K23" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="42">
+      <c r="B24" s="39">
         <v>4</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43">
+      <c r="C24" s="40"/>
+      <c r="D24" s="40">
         <v>2</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43">
+      <c r="E24" s="43"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40">
         <v>1</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
+      <c r="I24" s="43"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="56"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="61"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="63"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="44"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="40">
+      <c r="B26" s="45">
         <v>1</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="40">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="45">
         <v>2</v>
       </c>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41">
+      <c r="G26" s="46"/>
+      <c r="H26" s="46">
         <v>4</v>
       </c>
-      <c r="I26" s="44"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
+      <c r="I26" s="48"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="45"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="43"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="45"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="43"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="56"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="61"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -6229,6 +6273,11 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6251,36 +6300,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -7053,196 +7102,196 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="62" t="s">
+      <c r="D20" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="40">
+      <c r="B22" s="45">
         <v>3</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41">
+      <c r="C22" s="46"/>
+      <c r="D22" s="46">
         <v>1</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="46">
+      <c r="E22" s="48"/>
+      <c r="F22" s="49">
         <v>4</v>
       </c>
-      <c r="G22" s="47"/>
-      <c r="H22" s="41">
+      <c r="G22" s="50"/>
+      <c r="H22" s="46">
         <v>2</v>
       </c>
-      <c r="I22" s="44"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="45"/>
-      <c r="K23" s="63" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="43"/>
+      <c r="K23" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="50">
+      <c r="B24" s="57">
         <v>4</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51">
+      <c r="C24" s="58"/>
+      <c r="D24" s="58">
         <v>2</v>
       </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="42">
+      <c r="E24" s="60"/>
+      <c r="F24" s="39">
         <v>3</v>
       </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="51">
+      <c r="G24" s="40"/>
+      <c r="H24" s="58">
         <v>1</v>
       </c>
-      <c r="I24" s="54"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
+      <c r="I24" s="60"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="55"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="63"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="58">
+      <c r="B26" s="55">
         <v>1</v>
       </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="41">
+      <c r="C26" s="56"/>
+      <c r="D26" s="46">
         <v>3</v>
       </c>
-      <c r="E26" s="44"/>
-      <c r="F26" s="58">
+      <c r="E26" s="48"/>
+      <c r="F26" s="55">
         <v>2</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59">
+      <c r="G26" s="56"/>
+      <c r="H26" s="56">
         <v>4</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
+      <c r="I26" s="59"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="50"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="54"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="60"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="42">
+      <c r="B28" s="39">
         <v>2</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43">
+      <c r="C28" s="40"/>
+      <c r="D28" s="40">
         <v>4</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="42">
+      <c r="E28" s="43"/>
+      <c r="F28" s="39">
         <v>1</v>
       </c>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43">
+      <c r="G28" s="40"/>
+      <c r="H28" s="40">
         <v>3</v>
       </c>
-      <c r="I28" s="45"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
+      <c r="I28" s="43"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="56"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="61"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="44"/>
       <c r="K29" s="64" t="s">
         <v>58</v>
       </c>
@@ -7270,6 +7319,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="F24:G25"/>
     <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
     <mergeCell ref="B26:C27"/>
@@ -7280,16 +7339,6 @@
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="F24:G25"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ottawa_Visuals\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB089E-65C7-4226-958F-D9BDA2871FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DE5950-91E4-4FCB-A4AB-188570851B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,8 +41,50 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="3">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="3">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="188">
   <si>
     <t>Line/Column</t>
   </si>
@@ -466,16 +508,6 @@
 From Stage</t>
   </si>
   <si>
-    <t>Items Used
-Here
-(needed now)</t>
-  </si>
-  <si>
-    <t>Items
-Received Here
-(used later →)</t>
-  </si>
-  <si>
     <t>Puzzle /
 Challenge</t>
   </si>
@@ -500,15 +532,7 @@
     <t>Start of Backpack</t>
   </si>
   <si>
-    <t>Main compartment
-(top)</t>
-  </si>
-  <si>
     <t>–</t>
-  </si>
-  <si>
-    <t>Water bottle + stickers
-Welcome card with QR code</t>
   </si>
   <si>
     <t>Hidden numbers in
@@ -631,6 +655,29 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side water bottle pocket </t>
+  </si>
+  <si>
+    <t>Items Used Here
+(needed now)</t>
+  </si>
+  <si>
+    <t>Items Received Here
+(used later →)</t>
+  </si>
+  <si>
+    <t>Water bottle + stickers</t>
+  </si>
+  <si>
+    <t>Laminate and attached to the handle</t>
+  </si>
+  <si>
+    <t>Hints</t>
+  </si>
+  <si>
+    <t>Icon</t>
   </si>
 </sst>
 </file>
@@ -641,7 +688,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,62 +754,59 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF888888"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF222222"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF222222"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="10"/>
-      <color rgb="FF888888"/>
-      <name val="Arial"/>
+      <color rgb="FF7D5800"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF222222"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF555555"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF7D5800"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFAAAAAA"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -820,11 +864,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E35A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1022,7 +1061,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1047,6 +1086,84 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1068,143 +1185,35 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1626,6 +1635,80 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+</richValueRels>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1892,304 +1975,336 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="37.140625" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-    </row>
-    <row r="2" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="38"/>
+      <c r="J2" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="3" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+    </row>
+    <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="I3" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="J3" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="K3" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="L3" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="M3" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="N3" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="45">
+        <v>0</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="I4" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="54" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="45">
+        <v>1</v>
+      </c>
+      <c r="B5" s="45" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="D5" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="47" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
-        <v>0</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="F5" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="K4" s="27"/>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>1</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="G5" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="I5" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="J5" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="K5" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="21" t="s">
+      <c r="L5" s="53">
+        <v>2</v>
+      </c>
+      <c r="M5" s="53"/>
+      <c r="N5" s="54"/>
+    </row>
+    <row r="6" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45">
+        <v>2</v>
+      </c>
+      <c r="B6" s="45" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="E6" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="G6" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="H6" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="K5" s="27">
+      <c r="I6" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="L6" s="53">
         <v>3</v>
       </c>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29">
+      <c r="M6" s="53"/>
+      <c r="N6" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="45">
+        <v>3</v>
+      </c>
+      <c r="B7" s="45" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="L7" s="53">
         <v>2</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="K6" s="33">
-        <v>3</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <v>3</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="32" t="s">
+      <c r="M7" s="53"/>
+      <c r="N7" s="54" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="45">
+        <v>4</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G7" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" s="24" t="s">
+      <c r="D8" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="E8" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="F8" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="K7" s="27">
-        <v>2</v>
-      </c>
-      <c r="L7" s="28" t="s">
+      <c r="G8" s="49" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
+      <c r="H8" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="L8" s="53">
         <v>4</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="G8" s="31" t="s">
+      <c r="M8" s="53"/>
+      <c r="N8" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="K8" s="33">
-        <v>4</v>
-      </c>
-      <c r="L8" s="34" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35">
+    </row>
+    <row r="9" spans="1:14" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="45">
         <v>5</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K5:K9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
+    <dataValidation type="list" allowBlank="1" sqref="L5:L9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2582,83 +2697,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>26</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="U2" s="1">
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AI2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE2" s="1">
+      <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AI2" s="1">
+      <c r="AK2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
       <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -2729,79 +2844,79 @@
       </c>
       <c r="T3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AD3" s="1">
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2870,83 +2985,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="T4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA4" s="1">
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
       <c r="AK4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -3019,83 +3134,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="U5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="V5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="W5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="X5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Y5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AA5" s="1">
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AE5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
       <c r="AF5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AI5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -3168,83 +3283,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="T6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="U6" s="1">
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AJ6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA6" s="1">
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -3308,83 +3423,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="U7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="V7" s="1">
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y7" s="1">
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AF7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF7" s="1">
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AH7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AJ7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AJ7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AL7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -3455,83 +3570,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="U8" s="1">
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AD8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z8" s="1">
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -3595,83 +3710,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="V9" s="1">
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AF9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="1">
+      <c r="AK9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -3745,79 +3860,79 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="U10" s="1">
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA10" s="1">
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC10" s="1">
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AI10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AG10" s="1">
+      <c r="AJ10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
       <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3880,83 +3995,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="V11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
       <c r="AE11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AH11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AJ11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -4022,83 +4137,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="T12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="V12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="W12" s="1">
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y12" s="1">
+      <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD12" s="1">
+      <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AL12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -4161,83 +4276,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="Y13" s="1">
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AD13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AE13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
       <c r="AH13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -4304,83 +4419,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="Z14" s="1">
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -4443,83 +4558,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="U15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="W15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -4582,59 +4697,59 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -4642,23 +4757,23 @@
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -5128,116 +5243,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="45">
+      <c r="C29" s="12">
         <v>3</v>
       </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46">
+      <c r="D29" s="13"/>
+      <c r="E29" s="13">
         <v>1</v>
       </c>
-      <c r="F29" s="48"/>
-      <c r="G29" s="49">
+      <c r="F29" s="16"/>
+      <c r="G29" s="18">
         <v>4</v>
       </c>
-      <c r="H29" s="50"/>
-      <c r="I29" s="46">
+      <c r="H29" s="19"/>
+      <c r="I29" s="13">
         <v>2</v>
       </c>
-      <c r="J29" s="48"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="43"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="57">
+      <c r="C31" s="22">
         <v>4</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58">
+      <c r="D31" s="23"/>
+      <c r="E31" s="23">
         <v>2</v>
       </c>
-      <c r="F31" s="60"/>
-      <c r="G31" s="39">
+      <c r="F31" s="26"/>
+      <c r="G31" s="14">
         <v>3</v>
       </c>
-      <c r="H31" s="40"/>
-      <c r="I31" s="58">
+      <c r="H31" s="15"/>
+      <c r="I31" s="23">
         <v>1</v>
       </c>
-      <c r="J31" s="60"/>
+      <c r="J31" s="26"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="63"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="27"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="55">
+      <c r="C33" s="30">
         <v>1</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="46">
+      <c r="D33" s="31"/>
+      <c r="E33" s="13">
         <v>3</v>
       </c>
-      <c r="F33" s="48"/>
-      <c r="G33" s="55">
+      <c r="F33" s="16"/>
+      <c r="G33" s="30">
         <v>2</v>
       </c>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56">
+      <c r="H33" s="31"/>
+      <c r="I33" s="31">
         <v>4</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="32"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="60"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="39">
+      <c r="C35" s="14">
         <v>2</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40">
+      <c r="D35" s="15"/>
+      <c r="E35" s="15">
         <v>4</v>
       </c>
-      <c r="F35" s="43"/>
-      <c r="G35" s="39">
+      <c r="F35" s="17"/>
+      <c r="G35" s="14">
         <v>1</v>
       </c>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40">
+      <c r="H35" s="15"/>
+      <c r="I35" s="15">
         <v>3</v>
       </c>
-      <c r="J35" s="43"/>
+      <c r="J35" s="17"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="41"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="44"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -5246,6 +5361,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
     <mergeCell ref="C29:D30"/>
     <mergeCell ref="E29:F30"/>
     <mergeCell ref="G29:H30"/>
@@ -5254,14 +5377,6 @@
     <mergeCell ref="E31:F32"/>
     <mergeCell ref="G31:H32"/>
     <mergeCell ref="I31:J32"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5284,36 +5399,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -6086,179 +6201,184 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="48"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="43"/>
-      <c r="K23" s="53" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="17"/>
+      <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="39">
+      <c r="B24" s="14">
         <v>4</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15">
         <v>2</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40">
+      <c r="E24" s="17"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15">
         <v>1</v>
       </c>
-      <c r="I24" s="43"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="I24" s="17"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="44"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="33"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="45">
+      <c r="B26" s="12">
         <v>1</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="45">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46">
+      <c r="G26" s="13"/>
+      <c r="H26" s="13">
         <v>4</v>
       </c>
-      <c r="I26" s="48"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="I26" s="16"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="43"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="17"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="43"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="17"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -6273,11 +6393,6 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6300,36 +6415,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -7102,223 +7217,233 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="45">
+      <c r="B22" s="12">
         <v>3</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13">
         <v>1</v>
       </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="49">
+      <c r="E22" s="16"/>
+      <c r="F22" s="18">
         <v>4</v>
       </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="46">
+      <c r="G22" s="19"/>
+      <c r="H22" s="13">
         <v>2</v>
       </c>
-      <c r="I22" s="48"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="43"/>
-      <c r="K23" s="53" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="17"/>
+      <c r="K23" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="57">
+      <c r="B24" s="22">
         <v>4</v>
       </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58">
+      <c r="C24" s="23"/>
+      <c r="D24" s="23">
         <v>2</v>
       </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="39">
+      <c r="E24" s="26"/>
+      <c r="F24" s="14">
         <v>3</v>
       </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="58">
+      <c r="G24" s="15"/>
+      <c r="H24" s="23">
         <v>1</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="I24" s="26"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="61"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="63"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="27"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="55">
+      <c r="B26" s="30">
         <v>1</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="46">
+      <c r="C26" s="31"/>
+      <c r="D26" s="13">
         <v>3</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="55">
+      <c r="E26" s="16"/>
+      <c r="F26" s="30">
         <v>2</v>
       </c>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56">
+      <c r="G26" s="31"/>
+      <c r="H26" s="31">
         <v>4</v>
       </c>
-      <c r="I26" s="59"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="I26" s="32"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="57"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="60"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="26"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="39">
+      <c r="B28" s="14">
         <v>2</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15">
         <v>4</v>
       </c>
-      <c r="E28" s="43"/>
-      <c r="F28" s="39">
+      <c r="E28" s="17"/>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40">
+      <c r="G28" s="15"/>
+      <c r="H28" s="15">
         <v>3</v>
       </c>
-      <c r="I28" s="43"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
+      <c r="I28" s="17"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="44"/>
-      <c r="K29" s="64" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="33"/>
+      <c r="K29" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K31" s="64"/>
-      <c r="L31" s="64"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K29:P31"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I29"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="D20:P21"/>
     <mergeCell ref="B22:C23"/>
@@ -7329,16 +7454,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:E25"/>
     <mergeCell ref="F24:G25"/>
-    <mergeCell ref="K29:P31"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="F28:G29"/>
-    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ottawa_Visuals\EscapeBackpack\Hiking_Trip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DE5950-91E4-4FCB-A4AB-188570851B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF09F4F6-3189-484A-ABCF-D68987A98736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="Riddle" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +47,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="10">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -68,8 +69,57 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="10">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -79,12 +129,33 @@
     <bk>
       <rc t="1" v="2"/>
     </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="199">
   <si>
     <t>Line/Column</t>
   </si>
@@ -678,6 +749,885 @@
   </si>
   <si>
     <t>Icon</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Look closely at the water bottle that is on the side of the backpack.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the water bottle, you will find animals that might have something special on them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Some numbers are hidden on the animals. The order in which to put them might be related to the era of each animal.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7 4 9 [image1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The word search and sudoku should come in handy for the next lock. Feel free to use the pen provided to complete them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hint 2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Look closely at the note to help you complete the word search.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> For the word search, use the words underlined in the note to give you 2 numbers. The sudoku blue box will give you the last number. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7 3 4 [image2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Some items and information provided will not be needed for the next lock but to keep for later. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> In the card, there is a news clipping that has the information needed to open the next lock. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Look closely at the image in the news clipping. You are looking for a specific word related to the dog mentioned.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> M O O N (dog's name) [image3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hint 1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">You will have a lot of items now but you are missing a few pieces to use them. In the main compartment, you should find a clue and an item to unlock a new lock. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The periodic table might be helpful to get the next combination, some addition might be required. Feel free to use the calculator provided.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the card with the ISS drawing, there is a clue to use with the periodic table. The numbers at the top left of some elements should come in handy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3 2 6 
+K - No - W - N - P - H - Y - Si - Cs 
+19 + 102 + 74 + 7 + 15 + 1 + 39 + 14 + 55 = 326 [image4]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You now have collected additional items. With the new items and what you already have, you should be able to unlock the final lock on the backpack. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hint 2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Use the instructions to build the Lego satellite. With the note, the calculator and the Lego model, you should be able to solve the next problem. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The note indicates the equation, that the numbers you are looking for are scattered around and that a slight correction is needed.
+You should have all the numbers if you look at what you already have.
+The correction might come from the Lego model you built and some mysterious scribbles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4 1 4
+GM (401,926.91) can be found behind the calculator, v (7.7) can be found behind the news clipping, and Re (6,779) can be found on step 6 of the Lego instructions.
+Equation gives 401,926.91 /  (7.7 x 7.7) - 6,779 = 408
+The combination of the Lego satellite and the inscriptions at the back of the card by aligning the edges of the satellite with the red markings provides the correction. It gives + S I X.
+Solution is 408 + 6 = 414 [image5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have received new items that will help you get into one of the compartment of the pouch that was in the backpack. Those should be enough to unlock the next lock. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> After completing the puzzle, you should have some instructions on how to get the next combination. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The back of the puzzle tells you what to look for (Card Numbers of Canadian Born Players) and the hockey cards will give you the numbers needed. Again, feel free to use the calculator provided.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 0 2 
+Jaime Bourbonnais (#13) born in Mississauga (Ontario), Daryl Watts (#22) born in Toronto (Ontario), Jocelyne Larocque (#18) born in Ste. Anne (Manitoba) and Natalie Spooner (#49) born in Scarborough (Ontario). 13 + 22 + 18 + 49 = 102</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have received the last item to complete a puzzle that you've had for a while. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have 3 Lego puzzles to complete. You should already have information to help you put the results from the Lego puzzles in the right order. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The card you received tells you the order in which to put the numbers from the Lego puzzles.  
+For the square Lego puzzle, use the black tile on top to push/pull tiles to reveal the number. 
+For the flat Lego puzzle, use the green tile on top to push the orange tiles inside the puzzle and retrieve a hidden piece. 
+For the Lego puzzle made of different pieces, it makes a cube that will reveal 2 numbers to add. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 1 8
+Square puzzle reveals the number 5
+Flat puzzle gives you a small round tile with the number 1
+The cube when assembled shows 5 + 3 = 8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You should have collected a number of bags with Lego items in them, now might be the time to use them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The riddle in the notebook will help you find the combination needed to assemble the Lego items.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You are looking for the doctor. You can use the Lego parts to build the characters as you read the riddle to help you find his name.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> D I C K [image8]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The combination of the map and agenda should give you the information needed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Once you have assembled the map, the agenda will help you trace your steps for the day. The Lego characters you have previously built should help you find some houses.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> As explained in the note, the errands should be done first. Follow the steps on the map to discover the first number. Then the day is the second item.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 6 3 2
+6 3 correspond to the date, 2 is the number revealed by the errands. [image9]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> This is the final lock! You should have collected all the pieces needed to help you with it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You should have 4 numbers made out of Lego, you should be able to find clues to put them in the correct order.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Look back at previous clues/instructions, there should be hidden markings to help you order the Lego numbers based on their colour.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4 1 3 0</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -688,7 +1638,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -802,6 +1752,14 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF555555"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -1061,7 +2019,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1086,84 +2044,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1214,6 +2094,85 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1676,7 +2635,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1687,6 +2646,34 @@
   </rv>
   <rv s="0">
     <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1706,6 +2693,13 @@
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
 </richValueRels>
 </file>
 
@@ -1975,329 +2969,454 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="24" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="37.140625" customWidth="1"/>
+    <col min="13" max="13" width="138.5703125" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38" t="s">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="I3" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="J3" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="K3" s="44" t="s">
+      <c r="K3" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="M3" s="39" t="s">
+      <c r="M3" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="13" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45">
+      <c r="A4" s="19">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="54" t="s">
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45">
+    <row r="5" spans="1:14" ht="54" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="45" t="e" vm="1">
+      <c r="B5" s="19" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="50" t="s">
+      <c r="I5" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="L5" s="53">
+      <c r="L5" s="27">
         <v>2</v>
       </c>
-      <c r="M5" s="53"/>
-      <c r="N5" s="54"/>
-    </row>
-    <row r="6" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45">
+      <c r="M5" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="N5" s="28"/>
+    </row>
+    <row r="6" spans="1:14" ht="81" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="e" vm="2">
+      <c r="B6" s="19" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="I6" s="50" t="s">
+      <c r="I6" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="J6" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="27">
         <v>3</v>
       </c>
-      <c r="M6" s="53"/>
-      <c r="N6" s="54" t="s">
+      <c r="M6" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="N6" s="28" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45">
+    <row r="7" spans="1:14" ht="54" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>3</v>
       </c>
-      <c r="B7" s="45" t="e" vm="3">
+      <c r="B7" s="19" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="G7" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="50" t="s">
+      <c r="I7" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="51" t="s">
+      <c r="J7" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="K7" s="52" t="s">
+      <c r="K7" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="L7" s="53">
+      <c r="L7" s="27">
         <v>2</v>
       </c>
-      <c r="M7" s="53"/>
-      <c r="N7" s="54" t="s">
+      <c r="M7" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="N7" s="28" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45">
+    <row r="8" spans="1:14" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>4</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46" t="s">
+      <c r="B8" s="19" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="J8" s="51" t="s">
+      <c r="J8" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="K8" s="52" t="s">
+      <c r="K8" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="L8" s="53">
+      <c r="L8" s="27">
         <v>4</v>
       </c>
-      <c r="M8" s="53"/>
-      <c r="N8" s="54" t="s">
+      <c r="M8" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="N8" s="28" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45">
+    <row r="9" spans="1:14" ht="189" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>5</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="54"/>
+      <c r="B9" s="19" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="N9" s="28"/>
+    </row>
+    <row r="10" spans="1:14" ht="108" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="N10" s="28"/>
+    </row>
+    <row r="11" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="N11" s="28"/>
+    </row>
+    <row r="12" spans="1:14" ht="54" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="N12" s="28"/>
+    </row>
+    <row r="13" spans="1:14" ht="81" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="N13" s="28"/>
+    </row>
+    <row r="14" spans="1:14" ht="54" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>10</v>
+      </c>
+      <c r="B14" s="19" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="N14" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2329,7 +3448,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D260E2E-9366-4C07-AD85-6CF609B51D36}">
-  <dimension ref="A2:M17"/>
+  <dimension ref="A2:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2490,10 +3609,37 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C17">
         <f>C13-(C8+C10)/10</f>
         <v>11.93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19">
+        <v>17.05</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="29">
+        <f>B19/3</f>
+        <v>5.6833333333333336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>31.79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="29">
+        <f>B20/3</f>
+        <v>10.596666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -2697,83 +3843,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Z2" s="1">
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
       <c r="AK2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -2840,83 +3986,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="U3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="V3" s="1">
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AK3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
-      </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -2985,83 +4131,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="W4" s="1">
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="AD4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AF4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AG4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
       <c r="AI4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AJ4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -3134,83 +4280,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="X5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AI5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="Y5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AE5" s="1">
+      <c r="AJ5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -3283,83 +4429,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="U6" s="1">
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AH6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Y6" s="1">
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AK6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
       <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -3423,83 +4569,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="U7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="V7" s="1">
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AH7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA7" s="1">
+      <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AF7" s="1">
+      <c r="AK7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AJ7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AL7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -3570,83 +4716,83 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="T8" s="1">
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AK8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
-      </c>
-      <c r="U8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AL8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -3710,19 +4856,19 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="U9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3730,63 +4876,63 @@
       </c>
       <c r="X9" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z9" s="1">
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AD9" s="1">
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AJ9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AK9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
       <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -3860,79 +5006,79 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="U10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="V10" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="X10" s="1">
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AG10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="Y10" s="1">
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AK10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -3995,83 +5141,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AG11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y11" s="1">
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AI11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG11" s="1">
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -4137,79 +5283,79 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="T12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="V12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="W12" s="1">
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
       <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4276,83 +5422,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="T13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="U13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AB13" s="1">
+      <c r="AF13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AE13" s="1">
+      <c r="AG13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
       <c r="AH13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AI13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AK13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -4419,83 +5565,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="T14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="U14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="V14" s="1">
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AI14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="X14" s="1">
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AK14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
       <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -4558,83 +5704,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -4697,83 +5843,83 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -5243,116 +6389,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="12">
+      <c r="C29" s="45">
         <v>3</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13">
+      <c r="D29" s="35"/>
+      <c r="E29" s="35">
         <v>1</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="18">
+      <c r="F29" s="36"/>
+      <c r="G29" s="46">
         <v>4</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="13">
+      <c r="H29" s="47"/>
+      <c r="I29" s="35">
         <v>2</v>
       </c>
-      <c r="J29" s="16"/>
+      <c r="J29" s="36"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="17"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="38"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="22">
+      <c r="C31" s="33">
         <v>4</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23">
+      <c r="D31" s="34"/>
+      <c r="E31" s="34">
         <v>2</v>
       </c>
-      <c r="F31" s="26"/>
-      <c r="G31" s="14">
+      <c r="F31" s="40"/>
+      <c r="G31" s="41">
         <v>3</v>
       </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="23">
+      <c r="H31" s="37"/>
+      <c r="I31" s="34">
         <v>1</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="27"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="52"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <v>1</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="13">
+      <c r="D33" s="32"/>
+      <c r="E33" s="35">
         <v>3</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="30">
+      <c r="F33" s="36"/>
+      <c r="G33" s="31">
         <v>2</v>
       </c>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31">
+      <c r="H33" s="32"/>
+      <c r="I33" s="32">
         <v>4</v>
       </c>
-      <c r="J33" s="32"/>
+      <c r="J33" s="39"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="22"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="26"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="40"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="14">
+      <c r="C35" s="41">
         <v>2</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15">
+      <c r="D35" s="37"/>
+      <c r="E35" s="37">
         <v>4</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="14">
+      <c r="F35" s="38"/>
+      <c r="G35" s="41">
         <v>1</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15">
+      <c r="H35" s="37"/>
+      <c r="I35" s="37">
         <v>3</v>
       </c>
-      <c r="J35" s="17"/>
+      <c r="J35" s="38"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="33"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -5361,6 +6507,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:F34"/>
     <mergeCell ref="G33:H34"/>
@@ -5369,14 +6523,6 @@
     <mergeCell ref="E35:F36"/>
     <mergeCell ref="G35:H36"/>
     <mergeCell ref="I35:J36"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5399,36 +6545,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -6201,184 +7347,179 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="16"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
-      <c r="K23" s="35" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
+      <c r="K23" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="B24" s="41">
         <v>4</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15">
+      <c r="C24" s="37"/>
+      <c r="D24" s="37">
         <v>2</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15">
+      <c r="E24" s="38"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37">
         <v>1</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
+      <c r="I24" s="38"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="33"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="44"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
+      <c r="B26" s="45">
         <v>1</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="12">
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="45">
         <v>2</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13">
+      <c r="G26" s="35"/>
+      <c r="H26" s="35">
         <v>4</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
+      <c r="I26" s="36"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="17"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="17"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="H22:I23"/>
     <mergeCell ref="F22:G23"/>
@@ -6393,6 +7534,11 @@
     <mergeCell ref="D26:E27"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -6415,36 +7561,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -7217,223 +8363,233 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="12">
+      <c r="B22" s="45">
         <v>3</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13">
+      <c r="C22" s="35"/>
+      <c r="D22" s="35">
         <v>1</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="18">
+      <c r="E22" s="36"/>
+      <c r="F22" s="46">
         <v>4</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="13">
+      <c r="G22" s="47"/>
+      <c r="H22" s="35">
         <v>2</v>
       </c>
-      <c r="I22" s="16"/>
+      <c r="I22" s="36"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="17"/>
-      <c r="K23" s="35" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
+      <c r="K23" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22">
+      <c r="B24" s="33">
         <v>4</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23">
+      <c r="C24" s="34"/>
+      <c r="D24" s="34">
         <v>2</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="14">
+      <c r="E24" s="40"/>
+      <c r="F24" s="41">
         <v>3</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="23">
+      <c r="G24" s="37"/>
+      <c r="H24" s="34">
         <v>1</v>
       </c>
-      <c r="I24" s="26"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
+      <c r="I24" s="40"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="27"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <v>1</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="13">
+      <c r="C26" s="32"/>
+      <c r="D26" s="35">
         <v>3</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="30">
+      <c r="E26" s="36"/>
+      <c r="F26" s="31">
         <v>2</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31">
+      <c r="G26" s="32"/>
+      <c r="H26" s="32">
         <v>4</v>
       </c>
-      <c r="I26" s="32"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
+      <c r="I26" s="39"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="26"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="40"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+      <c r="B28" s="41">
         <v>2</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37">
         <v>4</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="14">
+      <c r="E28" s="38"/>
+      <c r="F28" s="41">
         <v>1</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15">
+      <c r="G28" s="37"/>
+      <c r="H28" s="37">
         <v>3</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
+      <c r="I28" s="38"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="33"/>
-      <c r="K29" s="36" t="s">
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
+      <c r="K29" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="36"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="P30" s="36"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-      <c r="P31" s="36"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="F24:G25"/>
     <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
     <mergeCell ref="B26:C27"/>
@@ -7444,16 +8600,6 @@
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="F24:G25"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF09F4F6-3189-484A-ABCF-D68987A98736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7A0C63-8DDD-40A3-A0C8-980B5248EC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,6 @@
     <sheet name="Riddle" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -155,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="212">
   <si>
     <t>Line/Column</t>
   </si>
@@ -553,46 +552,17 @@
     <t>🎒 Backpack Adventure – Master Tracker</t>
   </si>
   <si>
-    <t>── LOCATION ──</t>
-  </si>
-  <si>
-    <t>── ITEMS ──</t>
-  </si>
-  <si>
-    <t>── PUZZLE ──</t>
-  </si>
-  <si>
-    <t>── ANSWER ──</t>
-  </si>
-  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>Stage Name</t>
   </si>
   <si>
     <t>Location
 in Bag</t>
   </si>
   <si>
-    <t>← Comes
-From Stage</t>
-  </si>
-  <si>
-    <t>Puzzle /
-Challenge</t>
-  </si>
-  <si>
-    <t>Solution Logic</t>
-  </si>
-  <si>
     <t>Code /
 Answer</t>
   </si>
   <si>
-    <t>Unlocks →</t>
-  </si>
-  <si>
     <t>Difficulty
 (1–5)</t>
   </si>
@@ -600,24 +570,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Start of Backpack</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <t>Hidden numbers in
-animal stickers</t>
-  </si>
-  <si>
-    <t>Each sticker animal's geological era → one digit
-(order of eras = order of digits)</t>
-  </si>
-  <si>
     <t>7  4  9</t>
-  </si>
-  <si>
-    <t>Front Compartment</t>
   </si>
   <si>
     <t>Front zip
@@ -628,24 +581,7 @@
 Word search + sudoku page</t>
   </si>
   <si>
-    <t>Lego number (0 blue)
-Lego hobbies pieces
-Sticker with IV blue
-→ used in Stage 4</t>
-  </si>
-  <si>
-    <t>Word search + sudoku
-combo puzzle</t>
-  </si>
-  <si>
-    <t>Words in search draw digits 7 &amp; 3;
-highlighted sudoku box = 4</t>
-  </si>
-  <si>
     <t>7  3  4</t>
-  </si>
-  <si>
-    <t>Front Pocket</t>
   </si>
   <si>
     <t>Items for later placed here so player carries them without knowing why</t>
@@ -659,22 +595,7 @@
 News article about dog</t>
   </si>
   <si>
-    <t>Value of v (on back
-of news clipping)
-→ used in Stage 4</t>
-  </si>
-  <si>
-    <t>Find the dog's name
-on collar in photo</t>
-  </si>
-  <si>
-    <t>Dog collar in news article photo clearly reads MOON</t>
-  </si>
-  <si>
     <t>M O O N</t>
-  </si>
-  <si>
-    <t>Large Compartment</t>
   </si>
   <si>
     <t>Easy breather before the final hard stage</t>
@@ -682,10 +603,6 @@
   <si>
     <t>Main large
 compartment</t>
-  </si>
-  <si>
-    <t>Lego pieces from Stage 2
-Value of v from Stage 3</t>
   </si>
   <si>
     <t>Periodic table
@@ -693,39 +610,13 @@
 Calculator</t>
   </si>
   <si>
-    <t>Locked pouch + final bag
-ISS instructions + Note
-Lego cube
-Lego jobs pieces</t>
-  </si>
-  <si>
-    <t>Periodic table element
-lookup from ISS note</t>
-  </si>
-  <si>
-    <t>Sum atomic numbers of elements in ISS note
-(KNoWN PHYSiCS). Requires calculator + periodic table</t>
-  </si>
-  <si>
-    <t>6  2  3</t>
-  </si>
-  <si>
-    <t>Top Pocket (END 🎉)</t>
-  </si>
-  <si>
     <t>Hardest stage — player must use items collected in stages 2 &amp; 3</t>
   </si>
   <si>
-    <t>Introduction</t>
-  </si>
-  <si>
     <t>Main Handle</t>
   </si>
   <si>
     <t>Escape Backpack QR code card</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t xml:space="preserve">Side water bottle pocket </t>
@@ -737,9 +628,6 @@
   <si>
     <t>Items Received Here
 (used later →)</t>
-  </si>
-  <si>
-    <t>Water bottle + stickers</t>
   </si>
   <si>
     <t>Laminate and attached to the handle</t>
@@ -1629,6 +1517,171 @@
       <t xml:space="preserve"> 4 1 3 0</t>
     </r>
   </si>
+  <si>
+    <t>Main compartment inside pocket</t>
+  </si>
+  <si>
+    <t>Otter Puzzle
+PWHL players cards</t>
+  </si>
+  <si>
+    <t>Sum player cards' numbers for Canadian born hockey player (from note on back of assembled puzzle)</t>
+  </si>
+  <si>
+    <t>1 0 2</t>
+  </si>
+  <si>
+    <t>ISS equation note
+Calculator (GM value)
+New Clippings (v value)
+Lego satellite instructions (Re value)</t>
+  </si>
+  <si>
+    <t>Treasure Pouch</t>
+  </si>
+  <si>
+    <t>3 2 6</t>
+  </si>
+  <si>
+    <t>4 1 4</t>
+  </si>
+  <si>
+    <t>Items from before
+(needed now)</t>
+  </si>
+  <si>
+    <t>Puzzle and Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden numbers in animal stickers -&gt; one digit per animal. Order of the digit is the historical era of each animal (Dinosaur -&gt; Mammoth -&gt; Dog) </t>
+  </si>
+  <si>
+    <t>Word search grid using highlighted words in note -&gt; draw digits 7 &amp; 3. Sudoku solution in highlighted box gives 4</t>
+  </si>
+  <si>
+    <t>Grandparent card mentions "your dog", dog collar in news article photo clearly reads MOON.</t>
+  </si>
+  <si>
+    <t>Sum atomic numbers of elements in ISS note (KNoWN PHYSiCS).</t>
+  </si>
+  <si>
+    <t>Water bottle with stickers</t>
+  </si>
+  <si>
+    <t>Lego satellite pieces</t>
+  </si>
+  <si>
+    <t>Lego number (4 orange)
+Lego Pets pieces</t>
+  </si>
+  <si>
+    <t>Solve the equation on the note with the right correction:
+GM, Re and V values from previous items
+Build satellite to fit on the back of the note card to reveal "+ S I X"</t>
+  </si>
+  <si>
+    <t>Pouch main compartment</t>
+  </si>
+  <si>
+    <t>Solve all three lego puzzles (2 pushing tiles in the right spot/order and 1 re-assembling the lego cube)
+Order of the digit is provided in the grandparents' card</t>
+  </si>
+  <si>
+    <t>Lego Hair pieces</t>
+  </si>
+  <si>
+    <t>Locked pouch with next puzzles
+Final "Treasure" bag
+Lego satellite instructions + Brown B sticker
+ISS equation note
+Calculator (GM value)
+Lego cube
+Lego Jobs pieces</t>
+  </si>
+  <si>
+    <t>Notepad with hints (names, jobs, pets…)
+Lego Names pieces</t>
+  </si>
+  <si>
+    <t>Lego Head pieces</t>
+  </si>
+  <si>
+    <t>Lego Hobbies pieces
+Lego Jobs pieces
+Lego Pets pieces
+Lego Head pieces
+Lego Hair pieces</t>
+  </si>
+  <si>
+    <t>5 1 8</t>
+  </si>
+  <si>
+    <t>D I C K</t>
+  </si>
+  <si>
+    <t>Text on the notepad mentions looking for the doctor
+Use the hint to build the Lego characters and find the name of the doctor</t>
+  </si>
+  <si>
+    <t>Lego number (1 brown)
+Sticker with red C</t>
+  </si>
+  <si>
+    <t>Lego number (0 blue)
+Lego Hobbies pieces
+Sticker with blue D</t>
+  </si>
+  <si>
+    <t>Pouch back pocket</t>
+  </si>
+  <si>
+    <t>Pouch front pocket</t>
+  </si>
+  <si>
+    <t>Pouch inside pocket</t>
+  </si>
+  <si>
+    <t>City map pieces (x9)
+Agenda card</t>
+  </si>
+  <si>
+    <t>Sticker with orange A</t>
+  </si>
+  <si>
+    <t>Lego numbers of different colours
+A, B, C &amp; D stickers of same colours</t>
+  </si>
+  <si>
+    <t>6 3 2</t>
+  </si>
+  <si>
+    <t>Agenda card mentions a date and a need to run errands
+The date on the agenda cards gives the first 2 digits
+The agenda card aslo gives the order of the errands
+Tracing the errands on the assembled map draws the last digit</t>
+  </si>
+  <si>
+    <t>4 1 3 0</t>
+  </si>
+  <si>
+    <t>Value of v (on back of news clipping)
+Lego puzzle (flat brown)</t>
+  </si>
+  <si>
+    <t>Lego cube
+Lego flat puzzle
+Grandparents' card</t>
+  </si>
+  <si>
+    <t>Lego square puzzle</t>
+  </si>
+  <si>
+    <t>Lego number (3 red)</t>
+  </si>
+  <si>
+    <t>Put Lego numbers received before in the right order.
+Order is given by letter stickers (A, B, C &amp; D) in previous cards</t>
+  </si>
 </sst>
 </file>
 
@@ -1708,13 +1761,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF888888"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
@@ -1758,6 +1804,13 @@
     <font>
       <b/>
       <u/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Aptos"/>
@@ -1811,17 +1864,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D52"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB8560A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E35A8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1831,17 +1874,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDE8C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDE0F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -1852,6 +1885,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5A2781"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2019,7 +2076,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2044,104 +2101,71 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2156,13 +2180,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2182,6 +2233,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF5A2781"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2969,461 +3025,417 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="138.5703125" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="6" width="30.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="138.5703125" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="B2" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12" t="s">
+      <c r="D2" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-    </row>
-    <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="J2" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="13" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>0</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="54" x14ac:dyDescent="0.25">
+      <c r="A4" s="16">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="21">
+        <v>2</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="K4" s="22"/>
+    </row>
+    <row r="5" spans="1:11" ht="54" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="21">
+        <v>3</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="54" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="21">
+        <v>2</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="108" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I7" s="21">
+        <v>4</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="189" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="21">
+        <v>4</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="K8" s="22"/>
+    </row>
+    <row r="9" spans="1:11" ht="108" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>6</v>
+      </c>
+      <c r="B9" s="16" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="21">
+        <v>2</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="K9" s="22"/>
+    </row>
+    <row r="10" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
-        <v>0</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="28" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="54" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>1</v>
-      </c>
-      <c r="B5" s="19" t="e" vm="1">
+      <c r="H10" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="21">
+        <v>4</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="K10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="L5" s="27">
+      <c r="C11" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="I11" s="21">
+        <v>3</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="K11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" ht="108" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="I12" s="21">
+        <v>4</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="22"/>
+    </row>
+    <row r="13" spans="1:11" ht="54" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="I13" s="21">
         <v>2</v>
       </c>
-      <c r="M5" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="N5" s="28"/>
-    </row>
-    <row r="6" spans="1:14" ht="81" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>2</v>
-      </c>
-      <c r="B6" s="19" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="L6" s="27">
-        <v>3</v>
-      </c>
-      <c r="M6" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="54" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <v>3</v>
-      </c>
-      <c r="B7" s="19" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="L7" s="27">
-        <v>2</v>
-      </c>
-      <c r="M7" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="N7" s="28" t="s">
+      <c r="J13" s="17" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
-        <v>4</v>
-      </c>
-      <c r="B8" s="19" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="K8" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="L8" s="27">
-        <v>4</v>
-      </c>
-      <c r="M8" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="189" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <v>5</v>
-      </c>
-      <c r="B9" s="19" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="N9" s="28"/>
-    </row>
-    <row r="10" spans="1:14" ht="108" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
-        <v>6</v>
-      </c>
-      <c r="B10" s="19" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="N10" s="28"/>
-    </row>
-    <row r="11" spans="1:14" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>7</v>
-      </c>
-      <c r="B11" s="19" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="N11" s="28"/>
-    </row>
-    <row r="12" spans="1:14" ht="54" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
-        <v>8</v>
-      </c>
-      <c r="B12" s="19" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="N12" s="28"/>
-    </row>
-    <row r="13" spans="1:14" ht="81" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
-        <v>9</v>
-      </c>
-      <c r="B13" s="19" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="N13" s="28"/>
-    </row>
-    <row r="14" spans="1:14" ht="54" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>10</v>
-      </c>
-      <c r="B14" s="19" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="N14" s="28"/>
+      <c r="K13" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="L5:L9" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
+    <dataValidation type="list" allowBlank="1" sqref="I4:I13" xr:uid="{7DED192A-EA34-4354-885F-7C051375C938}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3431,6 +3443,9 @@
   <headerFooter>
     <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="H4:H5 H7:H8 H10 H12" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3617,7 +3632,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="B19">
         <v>17.05</v>
@@ -3625,7 +3640,7 @@
       <c r="C19" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="23">
         <f>B19/3</f>
         <v>5.6833333333333336</v>
       </c>
@@ -3637,7 +3652,7 @@
       <c r="C20" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="23">
         <f>B20/3</f>
         <v>10.596666666666666</v>
       </c>
@@ -3843,83 +3858,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="V2" s="1">
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AH2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X2" s="1">
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AJ2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
-      </c>
-      <c r="Y2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -3986,83 +4001,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>7</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="T3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="U3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="V3" s="1">
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AF3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="W3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AE3" s="1">
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AI3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
       <c r="AJ3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AK3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -4131,83 +4146,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>26</v>
       </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="V4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W4" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AB4" s="1">
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>26</v>
       </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AG4" s="1">
+      <c r="AL4" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -4280,83 +4295,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="U5" s="1">
+      <c r="V5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AG5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="V5" s="1">
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AI5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AJ5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="W5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="X5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Y5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
       <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -4429,83 +4444,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="T6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="U6" s="1">
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AF6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="W6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="X6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
       <c r="AG6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AL6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AI6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -4569,83 +4584,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="U7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AB7" s="1">
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AG7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AF7" s="1">
+      <c r="AH7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
       <c r="AI7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -4716,79 +4731,79 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="U8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="X8" s="1">
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ8" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
       <c r="AK8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4856,83 +4871,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="T9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="U9" s="1">
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH9" s="1">
+      <c r="AK9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
       <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -5002,83 +5017,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="V10" s="1">
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AK10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -5141,83 +5156,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="V11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Z11" s="1">
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AF11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AC11" s="1">
+      <c r="AG11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -5283,83 +5298,83 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="W12" s="1">
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AI12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Y12" s="1">
+      <c r="AJ12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ12" s="1">
+      <c r="AK12" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -5422,83 +5437,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="T13" s="1">
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AG13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="U13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AB13" s="1">
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF13" s="1">
+      <c r="AK13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AL13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -5565,83 +5580,83 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="U14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="V14" s="1">
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AI14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="W14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z14" s="1">
+      <c r="AJ14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AC14" s="1">
+      <c r="AK14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
       <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -5704,83 +5719,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="W15" s="1">
+      <c r="Z15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Z15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -5843,11 +5858,11 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -5855,39 +5870,39 @@
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -5895,31 +5910,31 @@
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -6389,116 +6404,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="45">
+      <c r="C29" s="29">
         <v>3</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35">
+      <c r="D29" s="30"/>
+      <c r="E29" s="30">
         <v>1</v>
       </c>
-      <c r="F29" s="36"/>
-      <c r="G29" s="46">
+      <c r="F29" s="33"/>
+      <c r="G29" s="35">
         <v>4</v>
       </c>
-      <c r="H29" s="47"/>
-      <c r="I29" s="35">
+      <c r="H29" s="36"/>
+      <c r="I29" s="30">
         <v>2</v>
       </c>
-      <c r="J29" s="36"/>
+      <c r="J29" s="33"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="41"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="38"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="34"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="33">
+      <c r="C31" s="39">
         <v>4</v>
       </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34">
+      <c r="D31" s="40"/>
+      <c r="E31" s="40">
         <v>2</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41">
+      <c r="F31" s="43"/>
+      <c r="G31" s="31">
         <v>3</v>
       </c>
-      <c r="H31" s="37"/>
-      <c r="I31" s="34">
+      <c r="H31" s="32"/>
+      <c r="I31" s="40">
         <v>1</v>
       </c>
-      <c r="J31" s="40"/>
+      <c r="J31" s="43"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="50"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="52"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="44"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="31">
+      <c r="C33" s="47">
         <v>1</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="35">
+      <c r="D33" s="48"/>
+      <c r="E33" s="30">
         <v>3</v>
       </c>
-      <c r="F33" s="36"/>
-      <c r="G33" s="31">
+      <c r="F33" s="33"/>
+      <c r="G33" s="47">
         <v>2</v>
       </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32">
+      <c r="H33" s="48"/>
+      <c r="I33" s="48">
         <v>4</v>
       </c>
-      <c r="J33" s="39"/>
+      <c r="J33" s="49"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="33"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="40"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="43"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="41">
+      <c r="C35" s="31">
         <v>2</v>
       </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37">
+      <c r="D35" s="32"/>
+      <c r="E35" s="32">
         <v>4</v>
       </c>
-      <c r="F35" s="38"/>
-      <c r="G35" s="41">
+      <c r="F35" s="34"/>
+      <c r="G35" s="31">
         <v>1</v>
       </c>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37">
+      <c r="H35" s="32"/>
+      <c r="I35" s="32">
         <v>3</v>
       </c>
-      <c r="J35" s="38"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="42"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="44"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="50"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -6507,6 +6522,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
     <mergeCell ref="C29:D30"/>
     <mergeCell ref="E29:F30"/>
     <mergeCell ref="G29:H30"/>
@@ -6515,14 +6538,6 @@
     <mergeCell ref="E31:F32"/>
     <mergeCell ref="G31:H32"/>
     <mergeCell ref="I31:J32"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -6535,46 +6550,1999 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D804ABF-C663-46F7-972D-D3A53183DCD1}">
   <sheetPr>
     <tabColor theme="8"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:Q29"/>
+  <dimension ref="B2:AI29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
     <col min="2" max="17" width="3.28515625" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" customWidth="1"/>
+    <col min="18" max="19" width="3.85546875" customWidth="1"/>
+    <col min="20" max="35" width="3.28515625" customWidth="1"/>
+    <col min="36" max="36" width="3.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="D2" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="V2" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+    </row>
+    <row r="3" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+    </row>
+    <row r="4" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI6" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI11" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI12" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI13" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI14" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI15" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI16" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI17" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI18" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="W20" s="51"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="51"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="51"/>
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="51"/>
+      <c r="AI20" s="1"/>
+    </row>
+    <row r="21" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="51"/>
+      <c r="W21" s="51"/>
+      <c r="X21" s="51"/>
+      <c r="Y21" s="51"/>
+      <c r="Z21" s="51"/>
+      <c r="AA21" s="51"/>
+      <c r="AB21" s="51"/>
+      <c r="AC21" s="51"/>
+      <c r="AD21" s="51"/>
+      <c r="AE21" s="51"/>
+      <c r="AF21" s="51"/>
+      <c r="AG21" s="51"/>
+      <c r="AH21" s="51"/>
+      <c r="AI21" s="1"/>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="33"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="33"/>
+    </row>
+    <row r="23" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="34"/>
+      <c r="K23" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="52"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="52"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="34"/>
+      <c r="AC23" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD23" s="52"/>
+      <c r="AE23" s="52"/>
+      <c r="AF23" s="52"/>
+      <c r="AG23" s="52"/>
+      <c r="AH23" s="52"/>
+      <c r="AI23" s="52"/>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B24" s="31">
+        <v>4</v>
+      </c>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32">
+        <v>2</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32">
+        <v>1</v>
+      </c>
+      <c r="I24" s="34"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="52"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="52"/>
+      <c r="T24" s="31">
+        <v>4</v>
+      </c>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32">
+        <v>2</v>
+      </c>
+      <c r="W24" s="34"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="34"/>
+      <c r="AC24" s="52"/>
+      <c r="AD24" s="52"/>
+      <c r="AE24" s="52"/>
+      <c r="AF24" s="52"/>
+      <c r="AG24" s="52"/>
+      <c r="AH24" s="52"/>
+      <c r="AI24" s="52"/>
+    </row>
+    <row r="25" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="50"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="52"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="52"/>
+      <c r="T25" s="45"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="45"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="50"/>
+      <c r="AC25" s="52"/>
+      <c r="AD25" s="52"/>
+      <c r="AE25" s="52"/>
+      <c r="AF25" s="52"/>
+      <c r="AG25" s="52"/>
+      <c r="AH25" s="52"/>
+      <c r="AI25" s="52"/>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B26" s="29">
+        <v>1</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="29">
+        <v>2</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30">
+        <v>4</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="52"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+      <c r="T26" s="29">
+        <v>1</v>
+      </c>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="33"/>
+      <c r="AC26" s="52"/>
+      <c r="AD26" s="52"/>
+      <c r="AE26" s="52"/>
+      <c r="AF26" s="52"/>
+      <c r="AG26" s="52"/>
+      <c r="AH26" s="52"/>
+      <c r="AI26" s="52"/>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="34"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="34"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="52"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="34"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="52"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="34"/>
+      <c r="AC28" s="52"/>
+      <c r="AD28" s="52"/>
+      <c r="AE28" s="52"/>
+      <c r="AF28" s="52"/>
+      <c r="AG28" s="52"/>
+      <c r="AH28" s="52"/>
+      <c r="AI28" s="52"/>
+    </row>
+    <row r="29" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="50"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="45"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="46"/>
+      <c r="AA29" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="Z28:AA29"/>
+    <mergeCell ref="V2:AH3"/>
+    <mergeCell ref="V20:AH21"/>
+    <mergeCell ref="T22:U23"/>
+    <mergeCell ref="V22:W23"/>
+    <mergeCell ref="X22:Y23"/>
+    <mergeCell ref="Z22:AA23"/>
+    <mergeCell ref="AC23:AI28"/>
+    <mergeCell ref="T24:U25"/>
+    <mergeCell ref="V24:W25"/>
+    <mergeCell ref="X24:Y25"/>
+    <mergeCell ref="Z24:AA25"/>
+    <mergeCell ref="T26:U27"/>
+    <mergeCell ref="V26:W27"/>
+    <mergeCell ref="X26:Y27"/>
+    <mergeCell ref="Z26:AA27"/>
+    <mergeCell ref="T28:U29"/>
+    <mergeCell ref="V28:W29"/>
+    <mergeCell ref="X28:Y29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="F24:G25"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I29"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFAF56D-3771-45EA-B0C5-14F1F62B7279}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="B2:Q31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="17" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -6623,7 +8591,7 @@
         <v>41</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
@@ -6673,7 +8641,7 @@
         <v>36</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
@@ -6723,7 +8691,7 @@
         <v>34</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
@@ -6773,7 +8741,7 @@
         <v>46</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
@@ -6873,7 +8841,7 @@
         <v>51</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
@@ -6923,7 +8891,7 @@
         <v>36</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -6973,7 +8941,7 @@
         <v>32</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
@@ -7023,7 +8991,7 @@
         <v>47</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
@@ -7073,7 +9041,7 @@
         <v>40</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
@@ -7123,7 +9091,7 @@
         <v>42</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
@@ -7173,7 +9141,7 @@
         <v>35</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
@@ -7223,7 +9191,7 @@
         <v>31</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -7273,7 +9241,7 @@
         <v>44</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -7323,7 +9291,7 @@
         <v>46</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -7347,1239 +9315,233 @@
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="45"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="29">
+        <v>3</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30">
+        <v>1</v>
+      </c>
+      <c r="E22" s="33"/>
+      <c r="F22" s="35">
+        <v>4</v>
+      </c>
+      <c r="G22" s="36"/>
+      <c r="H22" s="30">
+        <v>2</v>
+      </c>
+      <c r="I22" s="33"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="41"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="38"/>
-      <c r="K23" s="54" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="34"/>
+      <c r="K23" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="41">
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="52"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="52"/>
+    </row>
+    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="39">
         <v>4</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37">
+      <c r="C24" s="40"/>
+      <c r="D24" s="40">
         <v>2</v>
       </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37">
+      <c r="E24" s="43"/>
+      <c r="F24" s="31">
+        <v>3</v>
+      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="40">
         <v>1</v>
       </c>
-      <c r="I24" s="38"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="52"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="52"/>
+    </row>
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="44"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="54"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="45">
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="52"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="52"/>
+    </row>
+    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="47">
         <v>1</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="45">
+      <c r="C26" s="48"/>
+      <c r="D26" s="30">
+        <v>3</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="47">
         <v>2</v>
       </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35">
+      <c r="G26" s="48"/>
+      <c r="H26" s="48">
         <v>4</v>
       </c>
-      <c r="I26" s="36"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="41"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="38"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="41"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="44"/>
+      <c r="I26" s="49"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="52"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+    </row>
+    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="43"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+    </row>
+    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="31">
+        <v>2</v>
+      </c>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32">
+        <v>4</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="31">
+        <v>1</v>
+      </c>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32">
+        <v>3</v>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="52"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+    </row>
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="50"/>
+      <c r="K29" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="53"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="F24:G25"/>
+  <mergeCells count="20">
+    <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:E27"/>
     <mergeCell ref="F26:G27"/>
     <mergeCell ref="H26:I27"/>
-    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-  </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 UNCLASSIFIED - NON CLASSIFIÉ&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFAF56D-3771-45EA-B0C5-14F1F62B7279}">
-  <sheetPr>
-    <tabColor theme="8"/>
-  </sheetPr>
-  <dimension ref="B2:Q31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="17" width="3.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="45">
-        <v>3</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35">
-        <v>1</v>
-      </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="46">
-        <v>4</v>
-      </c>
-      <c r="G22" s="47"/>
-      <c r="H22" s="35">
-        <v>2</v>
-      </c>
-      <c r="I22" s="36"/>
-    </row>
-    <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="41"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="38"/>
-      <c r="K23" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-    </row>
-    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="33">
-        <v>4</v>
-      </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34">
-        <v>2</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41">
-        <v>3</v>
-      </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="34">
-        <v>1</v>
-      </c>
-      <c r="I24" s="40"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="54"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-    </row>
-    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="31">
-        <v>1</v>
-      </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="35">
-        <v>3</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="31">
-        <v>2</v>
-      </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32">
-        <v>4</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-    </row>
-    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="33"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="40"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-    </row>
-    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="41">
-        <v>2</v>
-      </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37">
-        <v>4</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="41">
-        <v>1</v>
-      </c>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37">
-        <v>3</v>
-      </c>
-      <c r="I28" s="38"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="44"/>
-      <c r="K29" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="L29" s="55"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="D20:P21"/>
     <mergeCell ref="B22:C23"/>
@@ -8590,16 +9552,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:E25"/>
     <mergeCell ref="F24:G25"/>
-    <mergeCell ref="K29:P31"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="F28:G29"/>
-    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Hiking_Trip/Support.xlsx
+++ b/Hiking_Trip/Support.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Hiking_Trip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7A0C63-8DDD-40A3-A0C8-980B5248EC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CB823D-F3A5-459C-BC0D-BF133B5CFD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="213">
   <si>
     <t>Line/Column</t>
   </si>
@@ -745,7 +745,428 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> The word search and sudoku should come in handy for the next lock. Feel free to use the pen provided to complete them.
+      <t xml:space="preserve"> You have received new items that will help you get into one of the compartment of the pouch that was in the backpack. Those should be enough to unlock the next lock. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> After completing the puzzle, you should have some instructions on how to get the next combination. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The back of the puzzle tells you what to look for (Card Numbers of Canadian Born Players) and the hockey cards will give you the numbers needed. Again, feel free to use the calculator provided.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 0 2 
+Jaime Bourbonnais (#13) born in Mississauga (Ontario), Daryl Watts (#22) born in Toronto (Ontario), Jocelyne Larocque (#18) born in Ste. Anne (Manitoba) and Natalie Spooner (#49) born in Scarborough (Ontario). 13 + 22 + 18 + 49 = 102</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You should have collected a number of bags with Lego items in them, now might be the time to use them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The riddle in the notebook will help you find the combination needed to assemble the Lego items.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You are looking for the doctor. You can use the Lego parts to build the characters as you read the riddle to help you find his name.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> D I C K [image8]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> This is the final lock! You should have collected all the pieces needed to help you with it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You should have 4 numbers made out of Lego, you should be able to find clues to put them in the correct order.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Look back at previous clues/instructions, there should be hidden markings to help you order the Lego numbers based on their colour.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4 1 3 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Main compartment inside pocket</t>
+  </si>
+  <si>
+    <t>Otter Puzzle
+PWHL players cards</t>
+  </si>
+  <si>
+    <t>Sum player cards' numbers for Canadian born hockey player (from note on back of assembled puzzle)</t>
+  </si>
+  <si>
+    <t>1 0 2</t>
+  </si>
+  <si>
+    <t>ISS equation note
+Calculator (GM value)
+New Clippings (v value)
+Lego satellite instructions (Re value)</t>
+  </si>
+  <si>
+    <t>Treasure Pouch</t>
+  </si>
+  <si>
+    <t>3 2 6</t>
+  </si>
+  <si>
+    <t>4 1 4</t>
+  </si>
+  <si>
+    <t>Items from before
+(needed now)</t>
+  </si>
+  <si>
+    <t>Puzzle and Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden numbers in animal stickers -&gt; one digit per animal. Order of the digit is the historical era of each animal (Dinosaur -&gt; Mammoth -&gt; Dog) </t>
+  </si>
+  <si>
+    <t>Word search grid using highlighted words in note -&gt; draw digits 7 &amp; 3. Sudoku solution in highlighted box gives 4</t>
+  </si>
+  <si>
+    <t>Grandparent card mentions "your dog", dog collar in news article photo clearly reads MOON.</t>
+  </si>
+  <si>
+    <t>Sum atomic numbers of elements in ISS note (KNoWN PHYSiCS).</t>
+  </si>
+  <si>
+    <t>Water bottle with stickers</t>
+  </si>
+  <si>
+    <t>Lego satellite pieces</t>
+  </si>
+  <si>
+    <t>Lego number (4 orange)
+Lego Pets pieces</t>
+  </si>
+  <si>
+    <t>Solve the equation on the note with the right correction:
+GM, Re and V values from previous items
+Build satellite to fit on the back of the note card to reveal "+ S I X"</t>
+  </si>
+  <si>
+    <t>Pouch main compartment</t>
+  </si>
+  <si>
+    <t>Solve all three lego puzzles (2 pushing tiles in the right spot/order and 1 re-assembling the lego cube)
+Order of the digit is provided in the grandparents' card</t>
+  </si>
+  <si>
+    <t>Lego Hair pieces</t>
+  </si>
+  <si>
+    <t>Locked pouch with next puzzles
+Final "Treasure" bag
+Lego satellite instructions + Brown B sticker
+ISS equation note
+Calculator (GM value)
+Lego cube
+Lego Jobs pieces</t>
+  </si>
+  <si>
+    <t>Notepad with hints (names, jobs, pets…)
+Lego Names pieces</t>
+  </si>
+  <si>
+    <t>Lego Head pieces</t>
+  </si>
+  <si>
+    <t>Lego Hobbies pieces
+Lego Jobs pieces
+Lego Pets pieces
+Lego Head pieces
+Lego Hair pieces</t>
+  </si>
+  <si>
+    <t>5 1 8</t>
+  </si>
+  <si>
+    <t>D I C K</t>
+  </si>
+  <si>
+    <t>Text on the notepad mentions looking for the doctor
+Use the hint to build the Lego characters and find the name of the doctor</t>
+  </si>
+  <si>
+    <t>Lego number (1 brown)
+Sticker with red C</t>
+  </si>
+  <si>
+    <t>Lego number (0 blue)
+Lego Hobbies pieces
+Sticker with blue D</t>
+  </si>
+  <si>
+    <t>Pouch back pocket</t>
+  </si>
+  <si>
+    <t>Pouch front pocket</t>
+  </si>
+  <si>
+    <t>Pouch inside pocket</t>
+  </si>
+  <si>
+    <t>City map pieces (x9)
+Agenda card</t>
+  </si>
+  <si>
+    <t>Sticker with orange A</t>
+  </si>
+  <si>
+    <t>Lego numbers of different colours
+A, B, C &amp; D stickers of same colours</t>
+  </si>
+  <si>
+    <t>6 3 2</t>
+  </si>
+  <si>
+    <t>Agenda card mentions a date and a need to run errands
+The date on the agenda cards gives the first 2 digits
+The agenda card aslo gives the order of the errands
+Tracing the errands on the assembled map draws the last digit</t>
+  </si>
+  <si>
+    <t>4 1 3 0</t>
+  </si>
+  <si>
+    <t>Value of v (on back of news clipping)
+Lego puzzle (flat brown)</t>
+  </si>
+  <si>
+    <t>Lego cube
+Lego flat puzzle
+Grandparents' card</t>
+  </si>
+  <si>
+    <t>Lego square puzzle</t>
+  </si>
+  <si>
+    <t>Lego number (3 red)</t>
+  </si>
+  <si>
+    <t>Put Lego numbers received before in the right order.
+Order is given by letter stickers (A, B, C &amp; D) in previous cards</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hint 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Some items and information provided will not be needed for the next lock but to keep for later. The word search and sudoku should come in handy for the next lock. Feel free to use the marker provided to complete them.
 </t>
     </r>
     <r>
@@ -830,7 +1251,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Some items and information provided will not be needed for the next lock but to keep for later. 
+      <t xml:space="preserve"> Some items and information provided will not be needed for the next lock but to keep for later. The "Thank You" card should have what all you need.
 </t>
     </r>
     <r>
@@ -915,7 +1336,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">You will have a lot of items now but you are missing a few pieces to use them. In the main compartment, you should find a clue and an item to unlock a new lock. 
+      <t xml:space="preserve">You will have a lot of items now but you are missing a few pieces to use them. In the main compartment, you should find a clue and an item to unlock the new lock. 
 </t>
     </r>
     <r>
@@ -1078,11 +1499,14 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 4 1 4
-GM (401,926.91) can be found behind the calculator, v (7.7) can be found behind the news clipping, and Re (6,779) can be found on step 6 of the Lego instructions.
+GM (401,926.91) can be found behind the calculator, v (7.7) can be found behind the news clipping, and Re (6,779) can be found on step 4 of the Lego instructions.
 Equation gives 401,926.91 /  (7.7 x 7.7) - 6,779 = 408
 The combination of the Lego satellite and the inscriptions at the back of the card by aligning the edges of the satellite with the red markings provides the correction. It gives + S I X.
 Solution is 408 + 6 = 414 [image5]</t>
     </r>
+  </si>
+  <si>
+    <t>Change hints names (titles) to be more vague</t>
   </si>
   <si>
     <r>
@@ -1103,7 +1527,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> You have received new items that will help you get into one of the compartment of the pouch that was in the backpack. Those should be enough to unlock the next lock. 
+      <t xml:space="preserve"> The combination of the map and agenda should give you the information needed.
 </t>
     </r>
     <r>
@@ -1124,7 +1548,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> After completing the puzzle, you should have some instructions on how to get the next combination. 
+      <t xml:space="preserve"> Once you have assembled the map, the agenda will help you trace your steps for the day. The Lego characters you have previously built should help you find some houses.
 </t>
     </r>
     <r>
@@ -1145,7 +1569,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> The back of the puzzle tells you what to look for (Card Numbers of Canadian Born Players) and the hockey cards will give you the numbers needed. Again, feel free to use the calculator provided.
+      <t xml:space="preserve"> The day gives you the first numbers. Follow the steps on the map to discover the last number. 
 </t>
     </r>
     <r>
@@ -1166,8 +1590,8 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1 0 2 
-Jaime Bourbonnais (#13) born in Mississauga (Ontario), Daryl Watts (#22) born in Toronto (Ontario), Jocelyne Larocque (#18) born in Ste. Anne (Manitoba) and Natalie Spooner (#49) born in Scarborough (Ontario). 13 + 22 + 18 + 49 = 102</t>
+      <t xml:space="preserve"> 6 3 2
+6 3 corresponds to the date, 2 is the number revealed by the errands. [image9]</t>
     </r>
   </si>
   <si>
@@ -1232,8 +1656,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> The card you received tells you the order in which to put the numbers from the Lego puzzles.  
-For the square Lego puzzle, use the black tile on top to push/pull tiles to reveal the number. 
-For the flat Lego puzzle, use the green tile on top to push the orange tiles inside the puzzle and retrieve a hidden piece. 
+For the blue square Lego puzzle, use the red tile on top to push/pull tiles to reveal the number. 
+For the flat brown Lego puzzle, use the green tile on top to push the orange tiles inside the puzzle and retrieve a hidden piece. 
 For the Lego puzzle made of different pieces, it makes a cube that will reveal 2 numbers to add. 
 </t>
     </r>
@@ -1258,429 +1682,8 @@
       <t xml:space="preserve"> 5 1 8
 Square puzzle reveals the number 5
 Flat puzzle gives you a small round tile with the number 1
-The cube when assembled shows 5 + 3 = 8</t>
+The cube when assembled shows 5 + 3 = 8 [image7]</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 1:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You should have collected a number of bags with Lego items in them, now might be the time to use them.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 2:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The riddle in the notebook will help you find the combination needed to assemble the Lego items.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 3:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You are looking for the doctor. You can use the Lego parts to build the characters as you read the riddle to help you find his name.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> D I C K [image8]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 1:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The combination of the map and agenda should give you the information needed.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 2:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Once you have assembled the map, the agenda will help you trace your steps for the day. The Lego characters you have previously built should help you find some houses.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 3:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> As explained in the note, the errands should be done first. Follow the steps on the map to discover the first number. Then the day is the second item.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 6 3 2
-6 3 correspond to the date, 2 is the number revealed by the errands. [image9]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 1:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> This is the final lock! You should have collected all the pieces needed to help you with it.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 2:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You should have 4 numbers made out of Lego, you should be able to find clues to put them in the correct order.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hint 3:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Look back at previous clues/instructions, there should be hidden markings to help you order the Lego numbers based on their colour.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4 1 3 0</t>
-    </r>
-  </si>
-  <si>
-    <t>Main compartment inside pocket</t>
-  </si>
-  <si>
-    <t>Otter Puzzle
-PWHL players cards</t>
-  </si>
-  <si>
-    <t>Sum player cards' numbers for Canadian born hockey player (from note on back of assembled puzzle)</t>
-  </si>
-  <si>
-    <t>1 0 2</t>
-  </si>
-  <si>
-    <t>ISS equation note
-Calculator (GM value)
-New Clippings (v value)
-Lego satellite instructions (Re value)</t>
-  </si>
-  <si>
-    <t>Treasure Pouch</t>
-  </si>
-  <si>
-    <t>3 2 6</t>
-  </si>
-  <si>
-    <t>4 1 4</t>
-  </si>
-  <si>
-    <t>Items from before
-(needed now)</t>
-  </si>
-  <si>
-    <t>Puzzle and Solution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden numbers in animal stickers -&gt; one digit per animal. Order of the digit is the historical era of each animal (Dinosaur -&gt; Mammoth -&gt; Dog) </t>
-  </si>
-  <si>
-    <t>Word search grid using highlighted words in note -&gt; draw digits 7 &amp; 3. Sudoku solution in highlighted box gives 4</t>
-  </si>
-  <si>
-    <t>Grandparent card mentions "your dog", dog collar in news article photo clearly reads MOON.</t>
-  </si>
-  <si>
-    <t>Sum atomic numbers of elements in ISS note (KNoWN PHYSiCS).</t>
-  </si>
-  <si>
-    <t>Water bottle with stickers</t>
-  </si>
-  <si>
-    <t>Lego satellite pieces</t>
-  </si>
-  <si>
-    <t>Lego number (4 orange)
-Lego Pets pieces</t>
-  </si>
-  <si>
-    <t>Solve the equation on the note with the right correction:
-GM, Re and V values from previous items
-Build satellite to fit on the back of the note card to reveal "+ S I X"</t>
-  </si>
-  <si>
-    <t>Pouch main compartment</t>
-  </si>
-  <si>
-    <t>Solve all three lego puzzles (2 pushing tiles in the right spot/order and 1 re-assembling the lego cube)
-Order of the digit is provided in the grandparents' card</t>
-  </si>
-  <si>
-    <t>Lego Hair pieces</t>
-  </si>
-  <si>
-    <t>Locked pouch with next puzzles
-Final "Treasure" bag
-Lego satellite instructions + Brown B sticker
-ISS equation note
-Calculator (GM value)
-Lego cube
-Lego Jobs pieces</t>
-  </si>
-  <si>
-    <t>Notepad with hints (names, jobs, pets…)
-Lego Names pieces</t>
-  </si>
-  <si>
-    <t>Lego Head pieces</t>
-  </si>
-  <si>
-    <t>Lego Hobbies pieces
-Lego Jobs pieces
-Lego Pets pieces
-Lego Head pieces
-Lego Hair pieces</t>
-  </si>
-  <si>
-    <t>5 1 8</t>
-  </si>
-  <si>
-    <t>D I C K</t>
-  </si>
-  <si>
-    <t>Text on the notepad mentions looking for the doctor
-Use the hint to build the Lego characters and find the name of the doctor</t>
-  </si>
-  <si>
-    <t>Lego number (1 brown)
-Sticker with red C</t>
-  </si>
-  <si>
-    <t>Lego number (0 blue)
-Lego Hobbies pieces
-Sticker with blue D</t>
-  </si>
-  <si>
-    <t>Pouch back pocket</t>
-  </si>
-  <si>
-    <t>Pouch front pocket</t>
-  </si>
-  <si>
-    <t>Pouch inside pocket</t>
-  </si>
-  <si>
-    <t>City map pieces (x9)
-Agenda card</t>
-  </si>
-  <si>
-    <t>Sticker with orange A</t>
-  </si>
-  <si>
-    <t>Lego numbers of different colours
-A, B, C &amp; D stickers of same colours</t>
-  </si>
-  <si>
-    <t>6 3 2</t>
-  </si>
-  <si>
-    <t>Agenda card mentions a date and a need to run errands
-The date on the agenda cards gives the first 2 digits
-The agenda card aslo gives the order of the errands
-Tracing the errands on the assembled map draws the last digit</t>
-  </si>
-  <si>
-    <t>4 1 3 0</t>
-  </si>
-  <si>
-    <t>Value of v (on back of news clipping)
-Lego puzzle (flat brown)</t>
-  </si>
-  <si>
-    <t>Lego cube
-Lego flat puzzle
-Grandparents' card</t>
-  </si>
-  <si>
-    <t>Lego square puzzle</t>
-  </si>
-  <si>
-    <t>Lego number (3 red)</t>
-  </si>
-  <si>
-    <t>Put Lego numbers received before in the right order.
-Order is given by letter stickers (A, B, C &amp; D) in previous cards</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1694,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1813,6 +1816,13 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF222222"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -2076,7 +2086,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2150,22 +2160,49 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2180,40 +2217,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2224,6 +2234,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3065,7 +3078,7 @@
         <v>133</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>152</v>
@@ -3074,7 +3087,7 @@
         <v>153</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>134</v>
@@ -3105,7 +3118,9 @@
       <c r="G3" s="17"/>
       <c r="H3" s="20"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="J3" s="54" t="s">
+        <v>210</v>
+      </c>
       <c r="K3" s="22" t="s">
         <v>154</v>
       </c>
@@ -3122,11 +3137,11 @@
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="18" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F4" s="19"/>
       <c r="G4" s="17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>137</v>
@@ -3139,7 +3154,7 @@
       </c>
       <c r="K4" s="22"/>
     </row>
-    <row r="5" spans="1:11" ht="54" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>2</v>
       </c>
@@ -3154,19 +3169,19 @@
         <v>139</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>140</v>
       </c>
       <c r="I5" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="K5" s="22" t="s">
         <v>141</v>
@@ -3187,19 +3202,19 @@
         <v>143</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>144</v>
       </c>
       <c r="I6" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>145</v>
@@ -3220,19 +3235,19 @@
         <v>147</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I7" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>148</v>
@@ -3246,28 +3261,28 @@
         <v>#VALUE!</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I8" s="21">
         <v>4</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="K8" s="22"/>
     </row>
@@ -3279,26 +3294,26 @@
         <v>#VALUE!</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="18" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I9" s="21">
         <v>2</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K9" s="22"/>
     </row>
@@ -3310,28 +3325,28 @@
         <v>#VALUE!</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G10" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="H10" s="24" t="s">
-        <v>193</v>
-      </c>
       <c r="I10" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="K10" s="22"/>
     </row>
@@ -3343,28 +3358,28 @@
         <v>#VALUE!</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E11" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>196</v>
-      </c>
       <c r="G11" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I11" s="21">
         <v>3</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K11" s="22"/>
     </row>
@@ -3376,26 +3391,26 @@
         <v>#VALUE!</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I12" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="K12" s="22"/>
     </row>
@@ -3407,26 +3422,26 @@
         <v>#VALUE!</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F13" s="19"/>
       <c r="G13" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I13" s="21">
         <v>2</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K13" s="22"/>
     </row>
@@ -3858,83 +3873,83 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:AL15" ca="1" si="0">MAX(ROUND(RAND()*26,0),1)</f>
+        <v>8</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="U2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="V2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="W2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="X2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Y2" s="1">
+      <c r="AD2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AH2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AJ2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AK2" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AL2" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
-      </c>
-      <c r="Z2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AB2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AE2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AG2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AH2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AJ2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
       </c>
       <c r="AN2" t="s">
         <v>5</v>
@@ -4001,83 +4016,83 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:AH16" ca="1" si="1">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="V3" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="W3" s="1">
+      <c r="Y3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AF3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AG3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AI3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AJ3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="X3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Y3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Z3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AA3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AB3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AE3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AF3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AG3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AI3" s="1">
+      <c r="AK3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AL3" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
-      </c>
-      <c r="AJ3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
       </c>
       <c r="AN3" t="s">
         <v>6</v>
@@ -4146,83 +4161,83 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AI4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AK4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AL4" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
-      </c>
-      <c r="T4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="U4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="V4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="W4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AA4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AG4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AH4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
       </c>
       <c r="AN4" t="s">
         <v>7</v>
@@ -4295,83 +4310,83 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="T5" s="1">
+      <c r="X5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AH5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AJ5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AK5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="U5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="V5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="W5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Y5" s="1">
+      <c r="AL5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
-      </c>
-      <c r="Z5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AB5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AG5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AI5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AJ5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AL5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
       </c>
       <c r="AN5" t="s">
         <v>8</v>
@@ -4444,83 +4459,83 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="W6" s="1">
+      <c r="AA6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AE6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="X6" s="1">
+      <c r="AF6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="Y6" s="1">
+      <c r="AG6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AH6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="Z6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AB6" s="1">
+      <c r="AI6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AJ6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="AC6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AD6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AE6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AF6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AG6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AI6" s="1">
+      <c r="AK6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AL6" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
       </c>
       <c r="AN6" t="s">
         <v>9</v>
@@ -4584,83 +4599,83 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U7" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="V7" s="1">
+      <c r="Z7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AH7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AI7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AJ7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="W7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="X7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AE7" s="1">
+      <c r="AK7" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="AF7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AG7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AJ7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
       <c r="AL7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AN7" t="s">
         <v>10</v>
@@ -4731,11 +4746,11 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4743,71 +4758,71 @@
       </c>
       <c r="V8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AH8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AI8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK8" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="Y8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Z8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AA8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AH8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AI8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AJ8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
       <c r="AL8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="s">
         <v>2</v>
@@ -4871,83 +4886,83 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="T9" s="1">
+      <c r="Y9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AJ9" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
       </c>
-      <c r="U9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="V9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Z9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AB9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AC9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="AD9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AE9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AF9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AG9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AH9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AI9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
       <c r="AK9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AN9" t="s">
         <v>11</v>
@@ -5017,83 +5032,83 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="W10" s="1">
+      <c r="Z10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AH10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AI10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AK10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="X10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG10" s="1">
+      <c r="AL10" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
       </c>
       <c r="AN10" t="s">
         <v>12</v>
@@ -5156,83 +5171,83 @@
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="T11" s="1">
+      <c r="V11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="W11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="U11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="X11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="W11" s="1">
+      <c r="AA11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AG11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="X11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Y11" s="1">
+      <c r="AH11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AI11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK11" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="Z11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
       <c r="AL11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AN11" t="s">
         <v>13</v>
@@ -5302,79 +5317,79 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK12" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="V12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="W12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
       <c r="AL12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AN12" t="s">
         <v>14</v>
@@ -5437,83 +5452,83 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="V13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AA13" s="1">
+      <c r="AG13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
       </c>
-      <c r="AB13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AG13" s="1">
+      <c r="AH13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AI13" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="AH13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
       <c r="AJ13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="s">
         <v>15</v>
@@ -5580,7 +5595,7 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -5588,75 +5603,75 @@
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="V14" s="1">
+      <c r="Z14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AD14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="W14" s="1">
+      <c r="AE14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AL14" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AH14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AI14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
       </c>
       <c r="AN14" t="s">
         <v>16</v>
@@ -5719,83 +5734,83 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AA15" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>22</v>
-      </c>
-      <c r="T15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="U15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="V15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="W15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="X15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="Y15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Z15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AA15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" ref="AB15:AL16" ca="1" si="2">MAX(ROUND(RAND()*26,0),1)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AE15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AN15" t="s">
         <v>17</v>
@@ -5858,7 +5873,7 @@
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -5870,71 +5885,71 @@
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AN16" t="s">
         <v>18</v>
@@ -6404,116 +6419,116 @@
     </row>
     <row r="28" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C29" s="29">
+      <c r="C29" s="43">
         <v>3</v>
       </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30">
+      <c r="D29" s="33"/>
+      <c r="E29" s="33">
         <v>1</v>
       </c>
-      <c r="F29" s="33"/>
-      <c r="G29" s="35">
+      <c r="F29" s="34"/>
+      <c r="G29" s="44">
         <v>4</v>
       </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="30">
+      <c r="H29" s="45"/>
+      <c r="I29" s="33">
         <v>2</v>
       </c>
-      <c r="J29" s="33"/>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C30" s="31"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="34"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="36"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="39">
+      <c r="C31" s="31">
         <v>4</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40">
+      <c r="D31" s="32"/>
+      <c r="E31" s="32">
         <v>2</v>
       </c>
-      <c r="F31" s="43"/>
-      <c r="G31" s="31">
+      <c r="F31" s="38"/>
+      <c r="G31" s="39">
         <v>3</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="40">
+      <c r="H31" s="35"/>
+      <c r="I31" s="32">
         <v>1</v>
       </c>
-      <c r="J31" s="43"/>
+      <c r="J31" s="38"/>
     </row>
     <row r="32" spans="1:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="44"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="50"/>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="47">
+      <c r="C33" s="29">
         <v>1</v>
       </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="30">
+      <c r="D33" s="30"/>
+      <c r="E33" s="33">
         <v>3</v>
       </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="47">
+      <c r="F33" s="34"/>
+      <c r="G33" s="29">
         <v>2</v>
       </c>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48">
+      <c r="H33" s="30"/>
+      <c r="I33" s="30">
         <v>4</v>
       </c>
-      <c r="J33" s="49"/>
+      <c r="J33" s="37"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="43"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="38"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="31">
+      <c r="C35" s="39">
         <v>2</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32">
+      <c r="D35" s="35"/>
+      <c r="E35" s="35">
         <v>4</v>
       </c>
-      <c r="F35" s="34"/>
-      <c r="G35" s="31">
+      <c r="F35" s="36"/>
+      <c r="G35" s="39">
         <v>1</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32">
+      <c r="H35" s="35"/>
+      <c r="I35" s="35">
         <v>3</v>
       </c>
-      <c r="J35" s="34"/>
+      <c r="J35" s="36"/>
     </row>
     <row r="36" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="45"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="50"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="42"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
@@ -6522,6 +6537,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:F34"/>
     <mergeCell ref="G33:H34"/>
@@ -6530,14 +6553,6 @@
     <mergeCell ref="E35:F36"/>
     <mergeCell ref="G35:H36"/>
     <mergeCell ref="I35:J36"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8199,32 +8214,32 @@
       <c r="AI21" s="1"/>
     </row>
     <row r="22" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="33"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="33"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="34"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="34"/>
     </row>
     <row r="23" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="34"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
       <c r="K23" s="52" t="s">
         <v>56</v>
       </c>
@@ -8234,14 +8249,14 @@
       <c r="O23" s="52"/>
       <c r="P23" s="52"/>
       <c r="Q23" s="52"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="34"/>
-      <c r="X23" s="37"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="34"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="47"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="36"/>
       <c r="AC23" s="52" t="s">
         <v>56</v>
       </c>
@@ -8253,20 +8268,20 @@
       <c r="AI23" s="52"/>
     </row>
     <row r="24" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B24" s="31">
+      <c r="B24" s="39">
         <v>4</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32">
+      <c r="C24" s="35"/>
+      <c r="D24" s="35">
         <v>2</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32">
+      <c r="E24" s="36"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35">
         <v>1</v>
       </c>
-      <c r="I24" s="34"/>
+      <c r="I24" s="36"/>
       <c r="K24" s="52"/>
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
@@ -8274,20 +8289,20 @@
       <c r="O24" s="52"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
-      <c r="T24" s="31">
+      <c r="T24" s="39">
         <v>4</v>
       </c>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32">
+      <c r="U24" s="35"/>
+      <c r="V24" s="35">
         <v>2</v>
       </c>
-      <c r="W24" s="34"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32">
+      <c r="W24" s="36"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35">
         <v>1</v>
       </c>
-      <c r="AA24" s="34"/>
+      <c r="AA24" s="36"/>
       <c r="AC24" s="52"/>
       <c r="AD24" s="52"/>
       <c r="AE24" s="52"/>
@@ -8297,14 +8312,14 @@
       <c r="AI24" s="52"/>
     </row>
     <row r="25" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="50"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
       <c r="K25" s="52"/>
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
@@ -8312,14 +8327,14 @@
       <c r="O25" s="52"/>
       <c r="P25" s="52"/>
       <c r="Q25" s="52"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="45"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="50"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="42"/>
+      <c r="X25" s="40"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="42"/>
       <c r="AC25" s="52"/>
       <c r="AD25" s="52"/>
       <c r="AE25" s="52"/>
@@ -8329,20 +8344,20 @@
       <c r="AI25" s="52"/>
     </row>
     <row r="26" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B26" s="29">
+      <c r="B26" s="43">
         <v>1</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="29">
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="43">
         <v>2</v>
       </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30">
+      <c r="G26" s="33"/>
+      <c r="H26" s="33">
         <v>4</v>
       </c>
-      <c r="I26" s="33"/>
+      <c r="I26" s="34"/>
       <c r="K26" s="52"/>
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
@@ -8350,20 +8365,20 @@
       <c r="O26" s="52"/>
       <c r="P26" s="52"/>
       <c r="Q26" s="52"/>
-      <c r="T26" s="29">
+      <c r="T26" s="43">
         <v>1</v>
       </c>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="29">
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="43">
         <v>2</v>
       </c>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30">
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33">
         <v>4</v>
       </c>
-      <c r="AA26" s="33"/>
+      <c r="AA26" s="34"/>
       <c r="AC26" s="52"/>
       <c r="AD26" s="52"/>
       <c r="AE26" s="52"/>
@@ -8373,14 +8388,14 @@
       <c r="AI26" s="52"/>
     </row>
     <row r="27" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="34"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="36"/>
       <c r="K27" s="52"/>
       <c r="L27" s="52"/>
       <c r="M27" s="52"/>
@@ -8388,14 +8403,14 @@
       <c r="O27" s="52"/>
       <c r="P27" s="52"/>
       <c r="Q27" s="52"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="34"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="36"/>
       <c r="AC27" s="52"/>
       <c r="AD27" s="52"/>
       <c r="AE27" s="52"/>
@@ -8405,14 +8420,14 @@
       <c r="AI27" s="52"/>
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="34"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="36"/>
       <c r="K28" s="52"/>
       <c r="L28" s="52"/>
       <c r="M28" s="52"/>
@@ -8420,14 +8435,14 @@
       <c r="O28" s="52"/>
       <c r="P28" s="52"/>
       <c r="Q28" s="52"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="34"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="36"/>
       <c r="AC28" s="52"/>
       <c r="AD28" s="52"/>
       <c r="AE28" s="52"/>
@@ -8437,25 +8452,47 @@
       <c r="AI28" s="52"/>
     </row>
     <row r="29" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="50"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="45"/>
-      <c r="Y29" s="46"/>
-      <c r="Z29" s="46"/>
-      <c r="AA29" s="50"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="42"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="F24:G25"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="T28:U29"/>
+    <mergeCell ref="V28:W29"/>
+    <mergeCell ref="X28:Y29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="H28:I29"/>
     <mergeCell ref="Z28:AA29"/>
     <mergeCell ref="V2:AH3"/>
     <mergeCell ref="V20:AH21"/>
@@ -8472,28 +8509,6 @@
     <mergeCell ref="V26:W27"/>
     <mergeCell ref="X26:Y27"/>
     <mergeCell ref="Z26:AA27"/>
-    <mergeCell ref="T28:U29"/>
-    <mergeCell ref="V28:W29"/>
-    <mergeCell ref="X28:Y29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="F24:G25"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="F28:G29"/>
-    <mergeCell ref="H28:I29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
@@ -9351,32 +9366,32 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="29">
+      <c r="B22" s="43">
         <v>3</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30">
+      <c r="C22" s="33"/>
+      <c r="D22" s="33">
         <v>1</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="35">
+      <c r="E22" s="34"/>
+      <c r="F22" s="44">
         <v>4</v>
       </c>
-      <c r="G22" s="36"/>
-      <c r="H22" s="30">
+      <c r="G22" s="45"/>
+      <c r="H22" s="33">
         <v>2</v>
       </c>
-      <c r="I22" s="33"/>
+      <c r="I22" s="34"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="34"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
       <c r="K23" s="52" t="s">
         <v>56</v>
       </c>
@@ -9388,22 +9403,22 @@
       <c r="Q23" s="52"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="39">
+      <c r="B24" s="31">
         <v>4</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40">
+      <c r="C24" s="32"/>
+      <c r="D24" s="32">
         <v>2</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="31">
+      <c r="E24" s="38"/>
+      <c r="F24" s="39">
         <v>3</v>
       </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="40">
+      <c r="G24" s="35"/>
+      <c r="H24" s="32">
         <v>1</v>
       </c>
-      <c r="I24" s="43"/>
+      <c r="I24" s="38"/>
       <c r="K24" s="52"/>
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
@@ -9413,14 +9428,14 @@
       <c r="Q24" s="52"/>
     </row>
     <row r="25" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="44"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
       <c r="K25" s="52"/>
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
@@ -9430,22 +9445,22 @@
       <c r="Q25" s="52"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="47">
+      <c r="B26" s="29">
         <v>1</v>
       </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="30">
+      <c r="C26" s="30"/>
+      <c r="D26" s="33">
         <v>3</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="47">
+      <c r="E26" s="34"/>
+      <c r="F26" s="29">
         <v>2</v>
       </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48">
+      <c r="G26" s="30"/>
+      <c r="H26" s="30">
         <v>4</v>
       </c>
-      <c r="I26" s="49"/>
+      <c r="I26" s="37"/>
       <c r="K26" s="52"/>
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
@@ -9455,14 +9470,14 @@
       <c r="Q26" s="52"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="43"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="38"/>
       <c r="K27" s="52"/>
       <c r="L27" s="52"/>
       <c r="M27" s="52"/>
@@ -9472,22 +9487,22 @@
       <c r="Q27" s="52"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="31">
+      <c r="B28" s="39">
         <v>2</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32">
+      <c r="C28" s="35"/>
+      <c r="D28" s="35">
         <v>4</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="31">
+      <c r="E28" s="36"/>
+      <c r="F28" s="39">
         <v>1</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32">
+      <c r="G28" s="35"/>
+      <c r="H28" s="35">
         <v>3</v>
       </c>
-      <c r="I28" s="34"/>
+      <c r="I28" s="36"/>
       <c r="K28" s="52"/>
       <c r="L28" s="52"/>
       <c r="M28" s="52"/>
@@ -9497,14 +9512,14 @@
       <c r="Q28" s="52"/>
     </row>
     <row r="29" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="50"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
       <c r="K29" s="53" t="s">
         <v>58</v>
       </c>
@@ -9532,6 +9547,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="D20:P21"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="K23:Q28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="F24:G25"/>
     <mergeCell ref="K29:P31"/>
     <mergeCell ref="H24:I25"/>
     <mergeCell ref="B26:C27"/>
@@ -9542,16 +9567,6 @@
     <mergeCell ref="D28:E29"/>
     <mergeCell ref="F28:G29"/>
     <mergeCell ref="H28:I29"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="D20:P21"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="K23:Q28"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="F24:G25"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
